--- a/compare/output/dscale_IndustryCO2_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_IndustryCO2_downscaled_SSP245.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>877.14508</v>
+        <v>693.0819</v>
       </c>
       <c r="F2" t="n">
-        <v>1657.109201</v>
+        <v>1331.733486</v>
       </c>
       <c r="G2" t="n">
-        <v>2730.518845</v>
+        <v>2283.331795</v>
       </c>
       <c r="H2" t="n">
-        <v>4244.829689</v>
+        <v>3719.314048</v>
       </c>
       <c r="I2" t="n">
-        <v>6257.110858</v>
+        <v>5802.441451</v>
       </c>
       <c r="J2" t="n">
         <v>8673.858603000001</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>128.463279</v>
+        <v>117.033357</v>
       </c>
       <c r="F3" t="n">
-        <v>192.798424</v>
+        <v>172.346238</v>
       </c>
       <c r="G3" t="n">
-        <v>283.91054</v>
+        <v>256.028744</v>
       </c>
       <c r="H3" t="n">
-        <v>413.114244</v>
+        <v>380.413089</v>
       </c>
       <c r="I3" t="n">
-        <v>582.108697</v>
+        <v>553.805306</v>
       </c>
       <c r="J3" t="n">
         <v>777.16166</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>501.504096</v>
+        <v>537.3489520000001</v>
       </c>
       <c r="F4" t="n">
-        <v>508.92642</v>
+        <v>552.357548</v>
       </c>
       <c r="G4" t="n">
-        <v>560.277237</v>
+        <v>601.4585939999999</v>
       </c>
       <c r="H4" t="n">
-        <v>660.56532</v>
+        <v>696.244066</v>
       </c>
       <c r="I4" t="n">
-        <v>784.4295980000001</v>
+        <v>808.566851</v>
       </c>
       <c r="J4" t="n">
         <v>893.95746</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>676.652917</v>
+        <v>563.010972</v>
       </c>
       <c r="F5" t="n">
-        <v>1281.455452</v>
+        <v>1082.922132</v>
       </c>
       <c r="G5" t="n">
-        <v>2199.874138</v>
+        <v>1937.185388</v>
       </c>
       <c r="H5" t="n">
-        <v>3514.086808</v>
+        <v>3215.94279</v>
       </c>
       <c r="I5" t="n">
-        <v>5223.292481</v>
+        <v>4968.619047</v>
       </c>
       <c r="J5" t="n">
         <v>7184.452611</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>22758.986284</v>
+        <v>22773.162867</v>
       </c>
       <c r="F6" t="n">
-        <v>31113.26853</v>
+        <v>31144.866061</v>
       </c>
       <c r="G6" t="n">
-        <v>41039.3915</v>
+        <v>40717.913561</v>
       </c>
       <c r="H6" t="n">
-        <v>54836.134754</v>
+        <v>54046.462684</v>
       </c>
       <c r="I6" t="n">
-        <v>72315.83164</v>
+        <v>71388.578536</v>
       </c>
       <c r="J6" t="n">
         <v>91116.641118</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>18950.410456</v>
+        <v>20037.378749</v>
       </c>
       <c r="F7" t="n">
-        <v>24327.226075</v>
+        <v>26444.032932</v>
       </c>
       <c r="G7" t="n">
-        <v>32235.446311</v>
+        <v>35708.876907</v>
       </c>
       <c r="H7" t="n">
-        <v>41601.143003</v>
+        <v>46305.582245</v>
       </c>
       <c r="I7" t="n">
-        <v>49994.281602</v>
+        <v>54504.362194</v>
       </c>
       <c r="J7" t="n">
         <v>53169.003344</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3659.915541</v>
+        <v>3343.937793</v>
       </c>
       <c r="F8" t="n">
-        <v>5799.634143</v>
+        <v>5233.448463</v>
       </c>
       <c r="G8" t="n">
-        <v>8848.855841000001</v>
+        <v>8062.570725</v>
       </c>
       <c r="H8" t="n">
-        <v>13194.875378</v>
+        <v>12248.492319</v>
       </c>
       <c r="I8" t="n">
-        <v>18896.301499</v>
+        <v>18053.581515</v>
       </c>
       <c r="J8" t="n">
         <v>25527.611385</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1022.136029</v>
+        <v>1105.343569</v>
       </c>
       <c r="F9" t="n">
-        <v>978.246839</v>
+        <v>1081.32145</v>
       </c>
       <c r="G9" t="n">
-        <v>996.329797</v>
+        <v>1092.846655</v>
       </c>
       <c r="H9" t="n">
-        <v>1086.463223</v>
+        <v>1165.863304</v>
       </c>
       <c r="I9" t="n">
-        <v>1207.37127</v>
+        <v>1257.761664</v>
       </c>
       <c r="J9" t="n">
         <v>1302.464333</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1477.8777</v>
+        <v>1222.889374</v>
       </c>
       <c r="F10" t="n">
-        <v>2575.634358</v>
+        <v>2121.45826</v>
       </c>
       <c r="G10" t="n">
-        <v>4055.43871</v>
+        <v>3423.824518</v>
       </c>
       <c r="H10" t="n">
-        <v>6221.735466</v>
+        <v>5468.846693</v>
       </c>
       <c r="I10" t="n">
-        <v>9204.952107999999</v>
+        <v>8542.959566</v>
       </c>
       <c r="J10" t="n">
         <v>12915.189304</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15490.811803</v>
+        <v>15690.491211</v>
       </c>
       <c r="F11" t="n">
-        <v>20372.29247</v>
+        <v>20665.302358</v>
       </c>
       <c r="G11" t="n">
-        <v>27321.648612</v>
+        <v>27722.080172</v>
       </c>
       <c r="H11" t="n">
-        <v>36787.639353</v>
+        <v>37272.69778</v>
       </c>
       <c r="I11" t="n">
-        <v>47834.747097</v>
+        <v>48241.081436</v>
       </c>
       <c r="J11" t="n">
         <v>58292.796606</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1021.541917</v>
+        <v>825.86603</v>
       </c>
       <c r="F12" t="n">
-        <v>1839.507035</v>
+        <v>1505.53895</v>
       </c>
       <c r="G12" t="n">
-        <v>2978.543935</v>
+        <v>2528.866309</v>
       </c>
       <c r="H12" t="n">
-        <v>4614.098845</v>
+        <v>4090.277738</v>
       </c>
       <c r="I12" t="n">
-        <v>6780.285991</v>
+        <v>6329.862674</v>
       </c>
       <c r="J12" t="n">
         <v>9318.488648</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7997.127498</v>
+        <v>7653.027825</v>
       </c>
       <c r="F13" t="n">
-        <v>11871.736356</v>
+        <v>11182.507425</v>
       </c>
       <c r="G13" t="n">
-        <v>17455.425794</v>
+        <v>16370.677892</v>
       </c>
       <c r="H13" t="n">
-        <v>25884.91742</v>
+        <v>24449.466747</v>
       </c>
       <c r="I13" t="n">
-        <v>37551.194273</v>
+        <v>36180.286874</v>
       </c>
       <c r="J13" t="n">
         <v>51778.196592</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>44272.151614</v>
+        <v>44312.101691</v>
       </c>
       <c r="F14" t="n">
-        <v>48575.447077</v>
+        <v>48654.245071</v>
       </c>
       <c r="G14" t="n">
-        <v>56367.46855</v>
+        <v>56497.311183</v>
       </c>
       <c r="H14" t="n">
-        <v>65030.478239</v>
+        <v>65220.655379</v>
       </c>
       <c r="I14" t="n">
-        <v>73986.921696</v>
+        <v>74243.23749100001</v>
       </c>
       <c r="J14" t="n">
-        <v>77834.872126</v>
+        <v>78140.21640200001</v>
       </c>
       <c r="K14" t="n">
-        <v>83225.566416</v>
+        <v>83585.070028</v>
       </c>
       <c r="L14" t="n">
-        <v>86441.103306</v>
+        <v>86846.15626600001</v>
       </c>
       <c r="M14" t="n">
-        <v>87578.287746</v>
+        <v>88021.43797499999</v>
       </c>
       <c r="N14" t="n">
-        <v>86910.73212299999</v>
+        <v>87386.026279</v>
       </c>
       <c r="O14" t="n">
-        <v>85242.07479499999</v>
+        <v>85746.453433</v>
       </c>
       <c r="P14" t="n">
-        <v>82738.32177</v>
+        <v>83269.58613700001</v>
       </c>
       <c r="Q14" t="n">
-        <v>80745.24808799999</v>
+        <v>81310.568744</v>
       </c>
       <c r="R14" t="n">
-        <v>78507.85054299999</v>
+        <v>79112.29797</v>
       </c>
       <c r="S14" t="n">
-        <v>76242.310145</v>
+        <v>76893.87270000001</v>
       </c>
       <c r="T14" t="n">
-        <v>74028.704081</v>
+        <v>74737.267333</v>
       </c>
       <c r="U14" t="n">
-        <v>71538.186015</v>
+        <v>72311.687819</v>
       </c>
       <c r="V14" t="n">
-        <v>68556.37396300001</v>
+        <v>69402.27243</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>59021.865112</v>
+        <v>59004.28769</v>
       </c>
       <c r="F15" t="n">
-        <v>71194.353947</v>
+        <v>71169.06980300001</v>
       </c>
       <c r="G15" t="n">
-        <v>86131.603495</v>
+        <v>86101.210756</v>
       </c>
       <c r="H15" t="n">
-        <v>101191.031139</v>
+        <v>101153.452492</v>
       </c>
       <c r="I15" t="n">
-        <v>116031.394981</v>
+        <v>115981.33641</v>
       </c>
       <c r="J15" t="n">
-        <v>122477.929461</v>
+        <v>122413.256821</v>
       </c>
       <c r="K15" t="n">
-        <v>131463.878854</v>
+        <v>131379.519682</v>
       </c>
       <c r="L15" t="n">
-        <v>137598.873828</v>
+        <v>137494.280865</v>
       </c>
       <c r="M15" t="n">
-        <v>141298.711742</v>
+        <v>141174.275949</v>
       </c>
       <c r="N15" t="n">
-        <v>142898.315094</v>
+        <v>142755.641396</v>
       </c>
       <c r="O15" t="n">
-        <v>143333.08384</v>
+        <v>143172.156416</v>
       </c>
       <c r="P15" t="n">
-        <v>142475.619587</v>
+        <v>142296.39897</v>
       </c>
       <c r="Q15" t="n">
-        <v>142314.065244</v>
+        <v>142112.804945</v>
       </c>
       <c r="R15" t="n">
-        <v>141465.12039</v>
+        <v>141237.772929</v>
       </c>
       <c r="S15" t="n">
-        <v>140327.362513</v>
+        <v>140068.474168</v>
       </c>
       <c r="T15" t="n">
-        <v>139081.467568</v>
+        <v>138783.587254</v>
       </c>
       <c r="U15" t="n">
-        <v>137255.877833</v>
+        <v>136911.334411</v>
       </c>
       <c r="V15" t="n">
-        <v>134741.560954</v>
+        <v>134340.588652</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>10535.322217</v>
+        <v>10546.769898</v>
       </c>
       <c r="F16" t="n">
-        <v>10032.10863</v>
+        <v>10047.903699</v>
       </c>
       <c r="G16" t="n">
-        <v>9809.478429999999</v>
+        <v>9823.548839999999</v>
       </c>
       <c r="H16" t="n">
-        <v>9936.205753</v>
+        <v>9945.544046000001</v>
       </c>
       <c r="I16" t="n">
-        <v>10381.774636</v>
+        <v>10385.476264</v>
       </c>
       <c r="J16" t="n">
-        <v>10396.312065</v>
+        <v>10394.616307</v>
       </c>
       <c r="K16" t="n">
-        <v>10865.283555</v>
+        <v>10859.20217</v>
       </c>
       <c r="L16" t="n">
-        <v>11242.652118</v>
+        <v>11233.37494</v>
       </c>
       <c r="M16" t="n">
-        <v>11508.798868</v>
+        <v>11497.910552</v>
       </c>
       <c r="N16" t="n">
-        <v>11635.052269</v>
+        <v>11623.782814</v>
       </c>
       <c r="O16" t="n">
-        <v>11670.043973</v>
+        <v>11658.760582</v>
       </c>
       <c r="P16" t="n">
-        <v>11586.551176</v>
+        <v>11575.060733</v>
       </c>
       <c r="Q16" t="n">
-        <v>11596.686348</v>
+        <v>11585.076528</v>
       </c>
       <c r="R16" t="n">
-        <v>11634.116069</v>
+        <v>11623.855147</v>
       </c>
       <c r="S16" t="n">
-        <v>11737.706836</v>
+        <v>11731.258064</v>
       </c>
       <c r="T16" t="n">
-        <v>11892.590611</v>
+        <v>11892.922728</v>
       </c>
       <c r="U16" t="n">
-        <v>12024.752786</v>
+        <v>12034.795419</v>
       </c>
       <c r="V16" t="n">
-        <v>12071.321165</v>
+        <v>12093.942583</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10574.496164</v>
+        <v>10541.343238</v>
       </c>
       <c r="F17" t="n">
-        <v>11994.12935</v>
+        <v>11924.644268</v>
       </c>
       <c r="G17" t="n">
-        <v>13880.138885</v>
+        <v>13767.580312</v>
       </c>
       <c r="H17" t="n">
-        <v>15710.5266</v>
+        <v>15552.245059</v>
       </c>
       <c r="I17" t="n">
-        <v>17442.266539</v>
+        <v>17238.248628</v>
       </c>
       <c r="J17" t="n">
-        <v>17822.973128</v>
+        <v>17589.087847</v>
       </c>
       <c r="K17" t="n">
-        <v>18589.22279</v>
+        <v>18322.351098</v>
       </c>
       <c r="L17" t="n">
-        <v>19062.17359</v>
+        <v>18768.933396</v>
       </c>
       <c r="M17" t="n">
-        <v>19400.826751</v>
+        <v>19087.766868</v>
       </c>
       <c r="N17" t="n">
-        <v>19630.354931</v>
+        <v>19303.289733</v>
       </c>
       <c r="O17" t="n">
-        <v>20126.957691</v>
+        <v>19791.650148</v>
       </c>
       <c r="P17" t="n">
-        <v>20710.726709</v>
+        <v>20371.702113</v>
       </c>
       <c r="Q17" t="n">
-        <v>21484.367252</v>
+        <v>21139.143598</v>
       </c>
       <c r="R17" t="n">
-        <v>22064.898449</v>
+        <v>21711.169656</v>
       </c>
       <c r="S17" t="n">
-        <v>22517.037907</v>
+        <v>22149.596749</v>
       </c>
       <c r="T17" t="n">
-        <v>22913.097854</v>
+        <v>22525.863001</v>
       </c>
       <c r="U17" t="n">
-        <v>23246.921143</v>
+        <v>22834.818257</v>
       </c>
       <c r="V17" t="n">
-        <v>23555.910732</v>
+        <v>23115.394052</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8244.647648</v>
+        <v>8243.980237</v>
       </c>
       <c r="F18" t="n">
-        <v>9586.832886</v>
+        <v>9587.009050000001</v>
       </c>
       <c r="G18" t="n">
-        <v>10801.261404</v>
+        <v>10800.299673</v>
       </c>
       <c r="H18" t="n">
-        <v>11917.981118</v>
+        <v>11914.325874</v>
       </c>
       <c r="I18" t="n">
-        <v>13122.394489</v>
+        <v>13116.453548</v>
       </c>
       <c r="J18" t="n">
-        <v>13682.458662</v>
+        <v>13677.368065</v>
       </c>
       <c r="K18" t="n">
-        <v>14690.586827</v>
+        <v>14688.395464</v>
       </c>
       <c r="L18" t="n">
-        <v>15426.465354</v>
+        <v>15428.52273</v>
       </c>
       <c r="M18" t="n">
-        <v>15719.633511</v>
+        <v>15724.867274</v>
       </c>
       <c r="N18" t="n">
-        <v>15510.038069</v>
+        <v>15515.752265</v>
       </c>
       <c r="O18" t="n">
-        <v>14948.981888</v>
+        <v>14952.121608</v>
       </c>
       <c r="P18" t="n">
-        <v>14171.29314</v>
+        <v>14169.764429</v>
       </c>
       <c r="Q18" t="n">
-        <v>13500.32885</v>
+        <v>13493.101967</v>
       </c>
       <c r="R18" t="n">
-        <v>12860.955842</v>
+        <v>12847.845591</v>
       </c>
       <c r="S18" t="n">
-        <v>12319.245762</v>
+        <v>12300.461483</v>
       </c>
       <c r="T18" t="n">
-        <v>11900.74006</v>
+        <v>11876.959858</v>
       </c>
       <c r="U18" t="n">
-        <v>11582.064288</v>
+        <v>11555.16616</v>
       </c>
       <c r="V18" t="n">
-        <v>11327.97891</v>
+        <v>11300.948007</v>
       </c>
     </row>
     <row r="19">
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>19170.004837</v>
+        <v>19489.312888</v>
       </c>
       <c r="F19" t="n">
-        <v>25041.017775</v>
+        <v>25885.263451</v>
       </c>
       <c r="G19" t="n">
-        <v>31129.921646</v>
+        <v>32766.769258</v>
       </c>
       <c r="H19" t="n">
-        <v>36653.958829</v>
+        <v>39389.564368</v>
       </c>
       <c r="I19" t="n">
-        <v>38994.516256</v>
+        <v>42815.066533</v>
       </c>
       <c r="J19" t="n">
         <v>30721.770231</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1181.678207</v>
+        <v>1188.587831</v>
       </c>
       <c r="F20" t="n">
-        <v>1522.094668</v>
+        <v>1541.123202</v>
       </c>
       <c r="G20" t="n">
-        <v>1979.530688</v>
+        <v>2024.119672</v>
       </c>
       <c r="H20" t="n">
-        <v>2434.104212</v>
+        <v>2517.395519</v>
       </c>
       <c r="I20" t="n">
-        <v>2755.52537</v>
+        <v>2876.507145</v>
       </c>
       <c r="J20" t="n">
         <v>2717.54711</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>170.748982</v>
+        <v>158.832028</v>
       </c>
       <c r="F21" t="n">
-        <v>239.19133</v>
+        <v>210.334514</v>
       </c>
       <c r="G21" t="n">
-        <v>345.859387</v>
+        <v>293.147351</v>
       </c>
       <c r="H21" t="n">
-        <v>518.878145</v>
+        <v>434.450253</v>
       </c>
       <c r="I21" t="n">
-        <v>811.5830989999999</v>
+        <v>697.527069</v>
       </c>
       <c r="J21" t="n">
         <v>1442.413257</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3750.887995</v>
+        <v>3681.273381</v>
       </c>
       <c r="F22" t="n">
-        <v>5458.21793</v>
+        <v>5284.242876</v>
       </c>
       <c r="G22" t="n">
-        <v>7657.837438</v>
+        <v>7326.181959</v>
       </c>
       <c r="H22" t="n">
-        <v>10508.007681</v>
+        <v>9949.043911999999</v>
       </c>
       <c r="I22" t="n">
-        <v>14373.214515</v>
+        <v>13578.058038</v>
       </c>
       <c r="J22" t="n">
         <v>21054.359335</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2856.387837</v>
+        <v>2828.26691</v>
       </c>
       <c r="F23" t="n">
-        <v>4271.472397</v>
+        <v>4201.062519</v>
       </c>
       <c r="G23" t="n">
-        <v>6262.760022</v>
+        <v>6131.981905</v>
       </c>
       <c r="H23" t="n">
-        <v>9017.970781</v>
+        <v>8809.329795</v>
       </c>
       <c r="I23" t="n">
-        <v>12624.972728</v>
+        <v>12347.350032</v>
       </c>
       <c r="J23" t="n">
         <v>17677.83117</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>923.142163</v>
+        <v>923.218762</v>
       </c>
       <c r="F24" t="n">
-        <v>1195.114356</v>
+        <v>1195.359966</v>
       </c>
       <c r="G24" t="n">
-        <v>1545.648046</v>
+        <v>1548.119645</v>
       </c>
       <c r="H24" t="n">
-        <v>1935.791584</v>
+        <v>1941.713612</v>
       </c>
       <c r="I24" t="n">
-        <v>2323.947738</v>
+        <v>2332.221855</v>
       </c>
       <c r="J24" t="n">
         <v>2712.239439</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>344.358203</v>
+        <v>342.022012</v>
       </c>
       <c r="F25" t="n">
-        <v>423.615031</v>
+        <v>417.039153</v>
       </c>
       <c r="G25" t="n">
-        <v>536.148727</v>
+        <v>523.600568</v>
       </c>
       <c r="H25" t="n">
-        <v>689.3114399999999</v>
+        <v>669.777322</v>
       </c>
       <c r="I25" t="n">
-        <v>878.685488</v>
+        <v>853.85892</v>
       </c>
       <c r="J25" t="n">
         <v>1142.462962</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5453.852297</v>
+        <v>5222.74345</v>
       </c>
       <c r="F26" t="n">
-        <v>8176.001654</v>
+        <v>7558.029747</v>
       </c>
       <c r="G26" t="n">
-        <v>11906.309532</v>
+        <v>10663.353704</v>
       </c>
       <c r="H26" t="n">
-        <v>17602.776133</v>
+        <v>15428.332403</v>
       </c>
       <c r="I26" t="n">
-        <v>27112.80665</v>
+        <v>23927.25193</v>
       </c>
       <c r="J26" t="n">
         <v>47835.7422</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3734.805145</v>
+        <v>3712.506711</v>
       </c>
       <c r="F27" t="n">
-        <v>5199.930075</v>
+        <v>5140.148946</v>
       </c>
       <c r="G27" t="n">
-        <v>6901.773428</v>
+        <v>6766.829406</v>
       </c>
       <c r="H27" t="n">
-        <v>9148.203224000001</v>
+        <v>8888.825984999999</v>
       </c>
       <c r="I27" t="n">
-        <v>12196.178345</v>
+        <v>11794.355834</v>
       </c>
       <c r="J27" t="n">
         <v>17088.18873</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3147.53817</v>
+        <v>3186.639863</v>
       </c>
       <c r="F28" t="n">
-        <v>3762.35421</v>
+        <v>3856.405053</v>
       </c>
       <c r="G28" t="n">
-        <v>4981.748778</v>
+        <v>5203.434226</v>
       </c>
       <c r="H28" t="n">
-        <v>6496.974902</v>
+        <v>6977.543759</v>
       </c>
       <c r="I28" t="n">
-        <v>7430.828953</v>
+        <v>8280.061785</v>
       </c>
       <c r="J28" t="n">
         <v>5108.605108</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1783.119743</v>
+        <v>1748.581943</v>
       </c>
       <c r="F29" t="n">
-        <v>2427.209187</v>
+        <v>2327.392166</v>
       </c>
       <c r="G29" t="n">
-        <v>3583.415568</v>
+        <v>3365.069689</v>
       </c>
       <c r="H29" t="n">
-        <v>5288.165074</v>
+        <v>4876.836066</v>
       </c>
       <c r="I29" t="n">
-        <v>7883.797305</v>
+        <v>7227.122582</v>
       </c>
       <c r="J29" t="n">
         <v>12909.460948</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2120.64024</v>
+        <v>2039.392654</v>
       </c>
       <c r="F30" t="n">
-        <v>2891.353923</v>
+        <v>2664.152156</v>
       </c>
       <c r="G30" t="n">
-        <v>4371.942419</v>
+        <v>3876.93418</v>
       </c>
       <c r="H30" t="n">
-        <v>6908.259177</v>
+        <v>5970.054004</v>
       </c>
       <c r="I30" t="n">
-        <v>11300.63041</v>
+        <v>9793.543717</v>
       </c>
       <c r="J30" t="n">
         <v>21233.014636</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>141.519856</v>
+        <v>112.558494</v>
       </c>
       <c r="F31" t="n">
-        <v>296.98364</v>
+        <v>220.29071</v>
       </c>
       <c r="G31" t="n">
-        <v>585.834357</v>
+        <v>426.178516</v>
       </c>
       <c r="H31" t="n">
-        <v>1112.764186</v>
+        <v>822.250421</v>
       </c>
       <c r="I31" t="n">
-        <v>2132.647907</v>
+        <v>1683.603229</v>
       </c>
       <c r="J31" t="n">
         <v>4649.958572</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5522.628805</v>
+        <v>5485.654519</v>
       </c>
       <c r="F32" t="n">
-        <v>6656.905316</v>
+        <v>6535.558325</v>
       </c>
       <c r="G32" t="n">
-        <v>8730.901081</v>
+        <v>8460.452637</v>
       </c>
       <c r="H32" t="n">
-        <v>11771.133549</v>
+        <v>11276.121419</v>
       </c>
       <c r="I32" t="n">
-        <v>16124.742993</v>
+        <v>15377.825054</v>
       </c>
       <c r="J32" t="n">
         <v>23197.113993</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6330.571484</v>
+        <v>6288.786045</v>
       </c>
       <c r="F33" t="n">
-        <v>8232.636815</v>
+        <v>8107.460311</v>
       </c>
       <c r="G33" t="n">
-        <v>11468.849798</v>
+        <v>11209.381812</v>
       </c>
       <c r="H33" t="n">
-        <v>15801.911289</v>
+        <v>15344.317368</v>
       </c>
       <c r="I33" t="n">
-        <v>21353.000507</v>
+        <v>20662.604151</v>
       </c>
       <c r="J33" t="n">
         <v>29395.116687</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2207.301083</v>
+        <v>1837.354417</v>
       </c>
       <c r="F34" t="n">
-        <v>5980.375083</v>
+        <v>4809.691079</v>
       </c>
       <c r="G34" t="n">
-        <v>14833.804413</v>
+        <v>11953.959798</v>
       </c>
       <c r="H34" t="n">
-        <v>31603.255338</v>
+        <v>25748.752476</v>
       </c>
       <c r="I34" t="n">
-        <v>61876.695143</v>
+        <v>52157.109976</v>
       </c>
       <c r="J34" t="n">
         <v>128237.447517</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4921.390807</v>
+        <v>4999.636621</v>
       </c>
       <c r="F35" t="n">
-        <v>7323.506144</v>
+        <v>7578.464124</v>
       </c>
       <c r="G35" t="n">
-        <v>11111.286138</v>
+        <v>11789.426615</v>
       </c>
       <c r="H35" t="n">
-        <v>14664.350306</v>
+        <v>16093.263929</v>
       </c>
       <c r="I35" t="n">
-        <v>15697.452124</v>
+        <v>18035.186223</v>
       </c>
       <c r="J35" t="n">
         <v>8755.257611000001</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>231.97058</v>
+        <v>231.287976</v>
       </c>
       <c r="F36" t="n">
-        <v>295.10279</v>
+        <v>293.268392</v>
       </c>
       <c r="G36" t="n">
-        <v>361.503605</v>
+        <v>356.697335</v>
       </c>
       <c r="H36" t="n">
-        <v>432.630239</v>
+        <v>422.094603</v>
       </c>
       <c r="I36" t="n">
-        <v>521.344819</v>
+        <v>503.043441</v>
       </c>
       <c r="J36" t="n">
         <v>675.728514</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7903.614582</v>
+        <v>8079.561772</v>
       </c>
       <c r="F37" t="n">
-        <v>8357.622562</v>
+        <v>8744.878462999999</v>
       </c>
       <c r="G37" t="n">
-        <v>9212.142591</v>
+        <v>9920.860027000001</v>
       </c>
       <c r="H37" t="n">
-        <v>9733.379606</v>
+        <v>10906.263756</v>
       </c>
       <c r="I37" t="n">
-        <v>8852.614448</v>
+        <v>10536.387023</v>
       </c>
       <c r="J37" t="n">
         <v>3142.245524</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6825.308967</v>
+        <v>6767.949298</v>
       </c>
       <c r="F38" t="n">
-        <v>9065.920758</v>
+        <v>8897.069106000001</v>
       </c>
       <c r="G38" t="n">
-        <v>12425.80631</v>
+        <v>12048.723999</v>
       </c>
       <c r="H38" t="n">
-        <v>17100.042266</v>
+        <v>16387.445116</v>
       </c>
       <c r="I38" t="n">
-        <v>23696.574836</v>
+        <v>22568.404383</v>
       </c>
       <c r="J38" t="n">
         <v>34769.446849</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1449.79119</v>
+        <v>1409.123144</v>
       </c>
       <c r="F39" t="n">
-        <v>1963.37078</v>
+        <v>1854.272744</v>
       </c>
       <c r="G39" t="n">
-        <v>2944.459976</v>
+        <v>2719.346058</v>
       </c>
       <c r="H39" t="n">
-        <v>4443.839781</v>
+        <v>4042.406945</v>
       </c>
       <c r="I39" t="n">
-        <v>6708.701263</v>
+        <v>6100.486857</v>
       </c>
       <c r="J39" t="n">
         <v>10984.782464</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>129.419269</v>
+        <v>120.005479</v>
       </c>
       <c r="F40" t="n">
-        <v>202.940339</v>
+        <v>178.023235</v>
       </c>
       <c r="G40" t="n">
-        <v>333.423079</v>
+        <v>281.604433</v>
       </c>
       <c r="H40" t="n">
-        <v>544.490225</v>
+        <v>450.884015</v>
       </c>
       <c r="I40" t="n">
-        <v>919.147354</v>
+        <v>775.029231</v>
       </c>
       <c r="J40" t="n">
         <v>1771.583193</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>183.726728</v>
+        <v>169.880457</v>
       </c>
       <c r="F41" t="n">
-        <v>313.519714</v>
+        <v>275.488257</v>
       </c>
       <c r="G41" t="n">
-        <v>528.342258</v>
+        <v>447.433624</v>
       </c>
       <c r="H41" t="n">
-        <v>876.94709</v>
+        <v>728.086622</v>
       </c>
       <c r="I41" t="n">
-        <v>1490.057361</v>
+        <v>1257.883148</v>
       </c>
       <c r="J41" t="n">
         <v>2891.9102</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7466.046135</v>
+        <v>7640.170047</v>
       </c>
       <c r="F42" t="n">
-        <v>8400.619999</v>
+        <v>8813.025153000001</v>
       </c>
       <c r="G42" t="n">
-        <v>9678.052548</v>
+        <v>10476.099776</v>
       </c>
       <c r="H42" t="n">
-        <v>10390.122905</v>
+        <v>11750.287028</v>
       </c>
       <c r="I42" t="n">
-        <v>9297.679387</v>
+        <v>11271.674778</v>
       </c>
       <c r="J42" t="n">
         <v>2454.031272</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>564.103493</v>
+        <v>549.995538</v>
       </c>
       <c r="F43" t="n">
-        <v>1016.412859</v>
+        <v>977.616566</v>
       </c>
       <c r="G43" t="n">
-        <v>1798.411382</v>
+        <v>1718.403896</v>
       </c>
       <c r="H43" t="n">
-        <v>2929.665455</v>
+        <v>2788.326166</v>
       </c>
       <c r="I43" t="n">
-        <v>4561.877932</v>
+        <v>4354.566503</v>
       </c>
       <c r="J43" t="n">
         <v>7069.253814</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1607.500162</v>
+        <v>1507.466877</v>
       </c>
       <c r="F44" t="n">
-        <v>2639.444363</v>
+        <v>2359.381718</v>
       </c>
       <c r="G44" t="n">
-        <v>4624.165017</v>
+        <v>4006.535934</v>
       </c>
       <c r="H44" t="n">
-        <v>8054.474302</v>
+        <v>6871.481215</v>
       </c>
       <c r="I44" t="n">
-        <v>14073.261999</v>
+        <v>12159.54954</v>
       </c>
       <c r="J44" t="n">
         <v>27181.368264</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1423.184103</v>
+        <v>1423.700836</v>
       </c>
       <c r="F45" t="n">
-        <v>1916.539352</v>
+        <v>1917.271478</v>
       </c>
       <c r="G45" t="n">
-        <v>2635.549062</v>
+        <v>2638.318408</v>
       </c>
       <c r="H45" t="n">
-        <v>3497.073005</v>
+        <v>3503.361333</v>
       </c>
       <c r="I45" t="n">
-        <v>4449.426539</v>
+        <v>4458.380156</v>
       </c>
       <c r="J45" t="n">
         <v>5451.438892</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>888.251875</v>
+        <v>795.436605</v>
       </c>
       <c r="F46" t="n">
-        <v>1659.940971</v>
+        <v>1392.210269</v>
       </c>
       <c r="G46" t="n">
-        <v>3235.067991</v>
+        <v>2620.89045</v>
       </c>
       <c r="H46" t="n">
-        <v>6208.379992</v>
+        <v>4979.59742</v>
       </c>
       <c r="I46" t="n">
-        <v>12051.728666</v>
+        <v>9968.073898000001</v>
       </c>
       <c r="J46" t="n">
         <v>26544.118793</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>96958.705692</v>
+        <v>97541.798236</v>
       </c>
       <c r="F47" t="n">
-        <v>141409.456214</v>
+        <v>143373.804927</v>
       </c>
       <c r="G47" t="n">
-        <v>200924.943954</v>
+        <v>205667.713512</v>
       </c>
       <c r="H47" t="n">
-        <v>269591.255866</v>
+        <v>279128.822467</v>
       </c>
       <c r="I47" t="n">
-        <v>335946.387784</v>
+        <v>351899.412526</v>
       </c>
       <c r="J47" t="n">
         <v>357951.434182</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6225.808445</v>
+        <v>6260.608068</v>
       </c>
       <c r="F48" t="n">
-        <v>7949.371177</v>
+        <v>8025.889887</v>
       </c>
       <c r="G48" t="n">
-        <v>10590.947776</v>
+        <v>10742.133023</v>
       </c>
       <c r="H48" t="n">
-        <v>13591.703073</v>
+        <v>13849.499659</v>
       </c>
       <c r="I48" t="n">
-        <v>16558.511261</v>
+        <v>16917.028813</v>
       </c>
       <c r="J48" t="n">
         <v>18779.006687</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>576.236163</v>
+        <v>539.297371</v>
       </c>
       <c r="F49" t="n">
-        <v>933.712707</v>
+        <v>833.086087</v>
       </c>
       <c r="G49" t="n">
-        <v>1538.935272</v>
+        <v>1324.876691</v>
       </c>
       <c r="H49" t="n">
-        <v>2504.359471</v>
+        <v>2109.637751</v>
       </c>
       <c r="I49" t="n">
-        <v>4178.341889</v>
+        <v>3560.33659</v>
       </c>
       <c r="J49" t="n">
         <v>7985.879924</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>42.536527</v>
+        <v>41.915463</v>
       </c>
       <c r="F50" t="n">
-        <v>55.623882</v>
+        <v>53.983825</v>
       </c>
       <c r="G50" t="n">
-        <v>72.832533</v>
+        <v>69.40133400000001</v>
       </c>
       <c r="H50" t="n">
-        <v>94.551222</v>
+        <v>88.29133299999999</v>
       </c>
       <c r="I50" t="n">
-        <v>125.591094</v>
+        <v>115.951221</v>
       </c>
       <c r="J50" t="n">
         <v>186.837374</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1588.654491</v>
+        <v>1518.370424</v>
       </c>
       <c r="F51" t="n">
-        <v>2255.429316</v>
+        <v>2061.018973</v>
       </c>
       <c r="G51" t="n">
-        <v>3482.441704</v>
+        <v>3061.127023</v>
       </c>
       <c r="H51" t="n">
-        <v>5506.43512</v>
+        <v>4712.972497</v>
       </c>
       <c r="I51" t="n">
-        <v>9090.893837</v>
+        <v>7823.825054</v>
       </c>
       <c r="J51" t="n">
         <v>17237.623419</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1088.598082</v>
+        <v>1072.096215</v>
       </c>
       <c r="F52" t="n">
-        <v>1284.787852</v>
+        <v>1235.487792</v>
       </c>
       <c r="G52" t="n">
-        <v>1668.845067</v>
+        <v>1560.335133</v>
       </c>
       <c r="H52" t="n">
-        <v>2297.503977</v>
+        <v>2095.638907</v>
       </c>
       <c r="I52" t="n">
-        <v>3335.967811</v>
+        <v>3020.046575</v>
       </c>
       <c r="J52" t="n">
         <v>5523.871787</v>
@@ -4478,58 +4478,58 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>78280.620052</v>
+        <v>78417.124956</v>
       </c>
       <c r="F54" t="n">
-        <v>78214.86368900001</v>
+        <v>78340.658859</v>
       </c>
       <c r="G54" t="n">
-        <v>84900.136457</v>
+        <v>85024.98547499999</v>
       </c>
       <c r="H54" t="n">
-        <v>88953.636038</v>
+        <v>89072.57460000001</v>
       </c>
       <c r="I54" t="n">
-        <v>91525.117176</v>
+        <v>91635.46447599999</v>
       </c>
       <c r="J54" t="n">
-        <v>97466.954482</v>
+        <v>97571.75347900001</v>
       </c>
       <c r="K54" t="n">
-        <v>106305.422487</v>
+        <v>106406.25376</v>
       </c>
       <c r="L54" t="n">
-        <v>110653.699159</v>
+        <v>110745.344548</v>
       </c>
       <c r="M54" t="n">
-        <v>111494.336472</v>
+        <v>111574.508884</v>
       </c>
       <c r="N54" t="n">
-        <v>110645.509608</v>
+        <v>110714.380703</v>
       </c>
       <c r="O54" t="n">
-        <v>108109.935343</v>
+        <v>108168.283089</v>
       </c>
       <c r="P54" t="n">
-        <v>103971.551798</v>
+        <v>104020.059778</v>
       </c>
       <c r="Q54" t="n">
-        <v>100092.150775</v>
+        <v>100132.208391</v>
       </c>
       <c r="R54" t="n">
-        <v>95961.337999</v>
+        <v>95993.893719</v>
       </c>
       <c r="S54" t="n">
-        <v>92436.151566</v>
+        <v>92462.328069</v>
       </c>
       <c r="T54" t="n">
-        <v>89556.92249899999</v>
+        <v>89577.703706</v>
       </c>
       <c r="U54" t="n">
-        <v>86952.17557000001</v>
+        <v>86968.356719</v>
       </c>
       <c r="V54" t="n">
-        <v>84238.153983</v>
+        <v>84250.27028899999</v>
       </c>
     </row>
     <row r="55">
@@ -4554,58 +4554,58 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>15209.463445</v>
+        <v>15072.958541</v>
       </c>
       <c r="F55" t="n">
-        <v>16045.113109</v>
+        <v>15919.317938</v>
       </c>
       <c r="G55" t="n">
-        <v>17710.565257</v>
+        <v>17585.716238</v>
       </c>
       <c r="H55" t="n">
-        <v>18615.23149</v>
+        <v>18496.292928</v>
       </c>
       <c r="I55" t="n">
-        <v>19076.872353</v>
+        <v>18966.525054</v>
       </c>
       <c r="J55" t="n">
-        <v>20139.106998</v>
+        <v>20034.308001</v>
       </c>
       <c r="K55" t="n">
-        <v>21692.248344</v>
+        <v>21591.417071</v>
       </c>
       <c r="L55" t="n">
-        <v>22230.688409</v>
+        <v>22139.043021</v>
       </c>
       <c r="M55" t="n">
-        <v>22015.581924</v>
+        <v>21935.409512</v>
       </c>
       <c r="N55" t="n">
-        <v>21465.010568</v>
+        <v>21396.139473</v>
       </c>
       <c r="O55" t="n">
-        <v>20654.124367</v>
+        <v>20595.776621</v>
       </c>
       <c r="P55" t="n">
-        <v>19610.754778</v>
+        <v>19562.246797</v>
       </c>
       <c r="Q55" t="n">
-        <v>18678.90666</v>
+        <v>18638.849044</v>
       </c>
       <c r="R55" t="n">
-        <v>17746.211264</v>
+        <v>17713.655544</v>
       </c>
       <c r="S55" t="n">
-        <v>16958.982322</v>
+        <v>16932.805819</v>
       </c>
       <c r="T55" t="n">
-        <v>16331.482055</v>
+        <v>16310.700848</v>
       </c>
       <c r="U55" t="n">
-        <v>15815.838995</v>
+        <v>15799.657846</v>
       </c>
       <c r="V55" t="n">
-        <v>15311.271641</v>
+        <v>15299.155335</v>
       </c>
     </row>
     <row r="56">
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>118.378711</v>
+        <v>110.458208</v>
       </c>
       <c r="F58" t="n">
-        <v>189.634297</v>
+        <v>174.157975</v>
       </c>
       <c r="G58" t="n">
-        <v>292.072599</v>
+        <v>270.47172</v>
       </c>
       <c r="H58" t="n">
-        <v>408.336357</v>
+        <v>384.906755</v>
       </c>
       <c r="I58" t="n">
-        <v>542.6736979999999</v>
+        <v>524.249555</v>
       </c>
       <c r="J58" t="n">
         <v>690.941434</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>57.861946</v>
+        <v>50.230396</v>
       </c>
       <c r="F59" t="n">
-        <v>118.366978</v>
+        <v>102.988024</v>
       </c>
       <c r="G59" t="n">
-        <v>205.753567</v>
+        <v>183.580419</v>
       </c>
       <c r="H59" t="n">
-        <v>309.31495</v>
+        <v>284.77719</v>
       </c>
       <c r="I59" t="n">
-        <v>433.27815</v>
+        <v>413.801602</v>
       </c>
       <c r="J59" t="n">
         <v>575.837001</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>144.256842</v>
+        <v>140.258928</v>
       </c>
       <c r="F60" t="n">
-        <v>170.08943</v>
+        <v>162.237352</v>
       </c>
       <c r="G60" t="n">
-        <v>215.199843</v>
+        <v>204.387955</v>
       </c>
       <c r="H60" t="n">
-        <v>266.163937</v>
+        <v>254.690952</v>
       </c>
       <c r="I60" t="n">
-        <v>324.596042</v>
+        <v>315.860414</v>
       </c>
       <c r="J60" t="n">
         <v>384.627173</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2547.865636</v>
+        <v>2482.030933</v>
       </c>
       <c r="F61" t="n">
-        <v>3453.991504</v>
+        <v>3331.541188</v>
       </c>
       <c r="G61" t="n">
-        <v>4664.291755</v>
+        <v>4502.663124</v>
       </c>
       <c r="H61" t="n">
-        <v>5908.530792</v>
+        <v>5737.421674</v>
       </c>
       <c r="I61" t="n">
-        <v>7268.407482</v>
+        <v>7134.137846</v>
       </c>
       <c r="J61" t="n">
         <v>8671.440973999999</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10585.281027</v>
+        <v>10580.944309</v>
       </c>
       <c r="F62" t="n">
-        <v>12859.856918</v>
+        <v>12956.530354</v>
       </c>
       <c r="G62" t="n">
-        <v>14978.650736</v>
+        <v>15255.100204</v>
       </c>
       <c r="H62" t="n">
-        <v>15779.435771</v>
+        <v>16161.729974</v>
       </c>
       <c r="I62" t="n">
-        <v>15585.58038</v>
+        <v>15904.271668</v>
       </c>
       <c r="J62" t="n">
         <v>14305.888477</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7088.374906</v>
+        <v>7003.93599</v>
       </c>
       <c r="F63" t="n">
-        <v>9144.722019000001</v>
+        <v>9020.253102999999</v>
       </c>
       <c r="G63" t="n">
-        <v>11488.947597</v>
+        <v>11363.134322</v>
       </c>
       <c r="H63" t="n">
-        <v>13565.076022</v>
+        <v>13455.802844</v>
       </c>
       <c r="I63" t="n">
-        <v>15640.959082</v>
+        <v>15572.150371</v>
       </c>
       <c r="J63" t="n">
         <v>17337.823697</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>20.926001</v>
+        <v>18.51169</v>
       </c>
       <c r="F64" t="n">
-        <v>37.975132</v>
+        <v>33.362593</v>
       </c>
       <c r="G64" t="n">
-        <v>61.715909</v>
+        <v>55.349704</v>
       </c>
       <c r="H64" t="n">
-        <v>88.813605</v>
+        <v>82.009159</v>
       </c>
       <c r="I64" t="n">
-        <v>120.59802</v>
+        <v>115.337924</v>
       </c>
       <c r="J64" t="n">
         <v>156.415323</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6015.942651</v>
+        <v>5769.137355</v>
       </c>
       <c r="F65" t="n">
-        <v>9187.807752999999</v>
+        <v>8708.666053000001</v>
       </c>
       <c r="G65" t="n">
-        <v>13635.119454</v>
+        <v>12980.021483</v>
       </c>
       <c r="H65" t="n">
-        <v>18544.954912</v>
+        <v>17842.719273</v>
       </c>
       <c r="I65" t="n">
-        <v>24088.09342</v>
+        <v>23538.851091</v>
       </c>
       <c r="J65" t="n">
         <v>29929.281386</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3887.400245</v>
+        <v>3795.428731</v>
       </c>
       <c r="F66" t="n">
-        <v>5434.442115</v>
+        <v>5270.299766</v>
       </c>
       <c r="G66" t="n">
-        <v>7512.505956</v>
+        <v>7315.121534</v>
       </c>
       <c r="H66" t="n">
-        <v>9570.373659000001</v>
+        <v>9384.093242999999</v>
       </c>
       <c r="I66" t="n">
-        <v>11666.200555</v>
+        <v>11535.677191</v>
       </c>
       <c r="J66" t="n">
         <v>13583.741726</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2069.713377</v>
+        <v>1891.434653</v>
       </c>
       <c r="F67" t="n">
-        <v>3660.410058</v>
+        <v>3315.174896</v>
       </c>
       <c r="G67" t="n">
-        <v>5926.344461</v>
+        <v>5450.604475</v>
       </c>
       <c r="H67" t="n">
-        <v>8494.842142</v>
+        <v>7990.699843</v>
       </c>
       <c r="I67" t="n">
-        <v>11394.875238</v>
+        <v>11010.828458</v>
       </c>
       <c r="J67" t="n">
         <v>14479.404317</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3121.540175</v>
+        <v>3138.238751</v>
       </c>
       <c r="F68" t="n">
-        <v>3806.972697</v>
+        <v>3872.981405</v>
       </c>
       <c r="G68" t="n">
-        <v>4724.825446</v>
+        <v>4892.729166</v>
       </c>
       <c r="H68" t="n">
-        <v>5157.133789</v>
+        <v>5409.090021</v>
       </c>
       <c r="I68" t="n">
-        <v>4963.252921</v>
+        <v>5193.787305</v>
       </c>
       <c r="J68" t="n">
         <v>4033.53168</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35.072591</v>
+        <v>30.84122</v>
       </c>
       <c r="F69" t="n">
-        <v>66.878581</v>
+        <v>58.629246</v>
       </c>
       <c r="G69" t="n">
-        <v>111.166762</v>
+        <v>99.576609</v>
       </c>
       <c r="H69" t="n">
-        <v>162.348064</v>
+        <v>149.769701</v>
       </c>
       <c r="I69" t="n">
-        <v>222.655792</v>
+        <v>212.828174</v>
       </c>
       <c r="J69" t="n">
         <v>291.226935</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1766.272496</v>
+        <v>1674.187892</v>
       </c>
       <c r="F70" t="n">
-        <v>2681.733532</v>
+        <v>2508.024509</v>
       </c>
       <c r="G70" t="n">
-        <v>3942.456752</v>
+        <v>3711.442459</v>
       </c>
       <c r="H70" t="n">
-        <v>5283.903217</v>
+        <v>5045.688879</v>
       </c>
       <c r="I70" t="n">
-        <v>6739.791312</v>
+        <v>6562.273863</v>
       </c>
       <c r="J70" t="n">
         <v>8196.710515999999</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3876.151393</v>
+        <v>3885.112698</v>
       </c>
       <c r="F71" t="n">
-        <v>4923.59508</v>
+        <v>4979.102825</v>
       </c>
       <c r="G71" t="n">
-        <v>5886.241326</v>
+        <v>6008.831033</v>
       </c>
       <c r="H71" t="n">
-        <v>6439.602661</v>
+        <v>6594.93716</v>
       </c>
       <c r="I71" t="n">
-        <v>6726.219143</v>
+        <v>6850.693612</v>
       </c>
       <c r="J71" t="n">
         <v>6683.85014</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2271.925516</v>
+        <v>2172.185705</v>
       </c>
       <c r="F72" t="n">
-        <v>3153.560928</v>
+        <v>2969.790373</v>
       </c>
       <c r="G72" t="n">
-        <v>4353.441207</v>
+        <v>4114.238442</v>
       </c>
       <c r="H72" t="n">
-        <v>5571.807911</v>
+        <v>5329.882193</v>
       </c>
       <c r="I72" t="n">
-        <v>6863.245973</v>
+        <v>6685.850535</v>
       </c>
       <c r="J72" t="n">
         <v>8128.128712</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>30093.321713</v>
+        <v>30959.817527</v>
       </c>
       <c r="F73" t="n">
-        <v>23340.517185</v>
+        <v>24771.483747</v>
       </c>
       <c r="G73" t="n">
-        <v>16452.133706</v>
+        <v>18049.965311</v>
       </c>
       <c r="H73" t="n">
-        <v>11182.329571</v>
+        <v>12631.433269</v>
       </c>
       <c r="I73" t="n">
-        <v>6778.762448</v>
+        <v>7793.665689</v>
       </c>
       <c r="J73" t="n">
         <v>1835.296218</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19.696956</v>
+        <v>17.227196</v>
       </c>
       <c r="F74" t="n">
-        <v>38.286069</v>
+        <v>33.616866</v>
       </c>
       <c r="G74" t="n">
-        <v>62.179098</v>
+        <v>55.828213</v>
       </c>
       <c r="H74" t="n">
-        <v>87.974898</v>
+        <v>81.29013</v>
       </c>
       <c r="I74" t="n">
-        <v>116.910242</v>
+        <v>111.834599</v>
       </c>
       <c r="J74" t="n">
         <v>148.280424</v>
@@ -6074,58 +6074,58 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2473.191709</v>
+        <v>2232.069332</v>
       </c>
       <c r="F75" t="n">
-        <v>2910.684573</v>
+        <v>2626.198983</v>
       </c>
       <c r="G75" t="n">
-        <v>3270.469486</v>
+        <v>2957.26476</v>
       </c>
       <c r="H75" t="n">
-        <v>3431.465856</v>
+        <v>3102.977768</v>
       </c>
       <c r="I75" t="n">
-        <v>3507.599416</v>
+        <v>3171.018103</v>
       </c>
       <c r="J75" t="n">
-        <v>3545.026306</v>
+        <v>3207.593471</v>
       </c>
       <c r="K75" t="n">
-        <v>3523.755367</v>
+        <v>3194.690539</v>
       </c>
       <c r="L75" t="n">
-        <v>3426.296696</v>
+        <v>3114.586885</v>
       </c>
       <c r="M75" t="n">
-        <v>3277.32352</v>
+        <v>2988.162185</v>
       </c>
       <c r="N75" t="n">
-        <v>3080.126679</v>
+        <v>2817.34047</v>
       </c>
       <c r="O75" t="n">
-        <v>2863.826906</v>
+        <v>2628.486114</v>
       </c>
       <c r="P75" t="n">
-        <v>2646.564522</v>
+        <v>2438.010683</v>
       </c>
       <c r="Q75" t="n">
-        <v>2467.409299</v>
+        <v>2281.975584</v>
       </c>
       <c r="R75" t="n">
-        <v>2304.526553</v>
+        <v>2140.498036</v>
       </c>
       <c r="S75" t="n">
-        <v>2171.415993</v>
+        <v>2026.443275</v>
       </c>
       <c r="T75" t="n">
-        <v>2075.491383</v>
+        <v>1947.291283</v>
       </c>
       <c r="U75" t="n">
-        <v>2014.641043</v>
+        <v>1901.862446</v>
       </c>
       <c r="V75" t="n">
-        <v>1975.763839</v>
+        <v>1878.709825</v>
       </c>
     </row>
     <row r="76">
@@ -6150,58 +6150,58 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11797.064192</v>
+        <v>11593.649332</v>
       </c>
       <c r="F76" t="n">
-        <v>13614.832487</v>
+        <v>13353.08882</v>
       </c>
       <c r="G76" t="n">
-        <v>14363.434298</v>
+        <v>13827.281124</v>
       </c>
       <c r="H76" t="n">
-        <v>14485.983381</v>
+        <v>13697.561026</v>
       </c>
       <c r="I76" t="n">
-        <v>14703.707509</v>
+        <v>13743.405349</v>
       </c>
       <c r="J76" t="n">
-        <v>15102.482906</v>
+        <v>14055.987427</v>
       </c>
       <c r="K76" t="n">
-        <v>15380.737046</v>
+        <v>14317.528279</v>
       </c>
       <c r="L76" t="n">
-        <v>15340.372126</v>
+        <v>14313.292987</v>
       </c>
       <c r="M76" t="n">
-        <v>15020.67875</v>
+        <v>14044.508176</v>
       </c>
       <c r="N76" t="n">
-        <v>14446.4508</v>
+        <v>13530.520407</v>
       </c>
       <c r="O76" t="n">
-        <v>13716.621232</v>
+        <v>12856.405316</v>
       </c>
       <c r="P76" t="n">
-        <v>12935.788456</v>
+        <v>12128.009914</v>
       </c>
       <c r="Q76" t="n">
-        <v>12309.742357</v>
+        <v>11543.946397</v>
       </c>
       <c r="R76" t="n">
-        <v>11739.099831</v>
+        <v>11016.788711</v>
       </c>
       <c r="S76" t="n">
-        <v>11287.029595</v>
+        <v>10612.0178</v>
       </c>
       <c r="T76" t="n">
-        <v>10977.786121</v>
+        <v>10354.928264</v>
       </c>
       <c r="U76" t="n">
-        <v>10785.446437</v>
+        <v>10222.036638</v>
       </c>
       <c r="V76" t="n">
-        <v>10629.443124</v>
+        <v>10137.446833</v>
       </c>
     </row>
     <row r="77">
@@ -6226,58 +6226,58 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5760.01831</v>
+        <v>5600.79239</v>
       </c>
       <c r="F77" t="n">
-        <v>6749.773044</v>
+        <v>6636.789312</v>
       </c>
       <c r="G77" t="n">
-        <v>7690.857057</v>
+        <v>7617.755297</v>
       </c>
       <c r="H77" t="n">
-        <v>7711.204763</v>
+        <v>7627.73148</v>
       </c>
       <c r="I77" t="n">
-        <v>7241.03009</v>
+        <v>7114.858862</v>
       </c>
       <c r="J77" t="n">
-        <v>6722.302863</v>
+        <v>6555.753433</v>
       </c>
       <c r="K77" t="n">
-        <v>6245.301023</v>
+        <v>6057.661222</v>
       </c>
       <c r="L77" t="n">
-        <v>5774.176897</v>
+        <v>5586.896672</v>
       </c>
       <c r="M77" t="n">
-        <v>5310.520886</v>
+        <v>5136.989187</v>
       </c>
       <c r="N77" t="n">
-        <v>4831.493008</v>
+        <v>4677.733731</v>
       </c>
       <c r="O77" t="n">
-        <v>4366.650829</v>
+        <v>4233.185611</v>
       </c>
       <c r="P77" t="n">
-        <v>3938.172786</v>
+        <v>3822.933049</v>
       </c>
       <c r="Q77" t="n">
-        <v>3595.820657</v>
+        <v>3495.32645</v>
       </c>
       <c r="R77" t="n">
-        <v>3296.064062</v>
+        <v>3208.610081</v>
       </c>
       <c r="S77" t="n">
-        <v>3049.670012</v>
+        <v>2973.628092</v>
       </c>
       <c r="T77" t="n">
-        <v>2860.101064</v>
+        <v>2793.933869</v>
       </c>
       <c r="U77" t="n">
-        <v>2720.500464</v>
+        <v>2663.083546</v>
       </c>
       <c r="V77" t="n">
-        <v>2609.837455</v>
+        <v>2560.942379</v>
       </c>
     </row>
     <row r="78">
@@ -6302,58 +6302,58 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>74735.773458</v>
+        <v>78289.833878</v>
       </c>
       <c r="F78" t="n">
-        <v>70096.965189</v>
+        <v>73473.599208</v>
       </c>
       <c r="G78" t="n">
-        <v>69720.305825</v>
+        <v>72555.257963</v>
       </c>
       <c r="H78" t="n">
-        <v>66755.460509</v>
+        <v>69014.771253</v>
       </c>
       <c r="I78" t="n">
-        <v>63770.662436</v>
+        <v>65659.967762</v>
       </c>
       <c r="J78" t="n">
-        <v>61576.281527</v>
+        <v>63287.571347</v>
       </c>
       <c r="K78" t="n">
-        <v>59527.22201</v>
+        <v>61161.46726</v>
       </c>
       <c r="L78" t="n">
-        <v>56863.896928</v>
+        <v>58430.442656</v>
       </c>
       <c r="M78" t="n">
-        <v>53837.837869</v>
+        <v>55329.277809</v>
       </c>
       <c r="N78" t="n">
-        <v>50377.651363</v>
+        <v>51775.445165</v>
       </c>
       <c r="O78" t="n">
-        <v>46715.268235</v>
+        <v>48016.088024</v>
       </c>
       <c r="P78" t="n">
-        <v>43074.275394</v>
+        <v>44275.660539</v>
       </c>
       <c r="Q78" t="n">
-        <v>40024.801279</v>
+        <v>41138.979222</v>
       </c>
       <c r="R78" t="n">
-        <v>37118.684289</v>
+        <v>38144.927837</v>
       </c>
       <c r="S78" t="n">
-        <v>34523.147845</v>
+        <v>35462.767235</v>
       </c>
       <c r="T78" t="n">
-        <v>32287.278825</v>
+        <v>33142.550813</v>
       </c>
       <c r="U78" t="n">
-        <v>30339.76107</v>
+        <v>31108.708878</v>
       </c>
       <c r="V78" t="n">
-        <v>28460.887997</v>
+        <v>29132.892936</v>
       </c>
     </row>
     <row r="79">
@@ -6378,58 +6378,58 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6054.168825</v>
+        <v>5547.664724</v>
       </c>
       <c r="F79" t="n">
-        <v>7790.447768</v>
+        <v>7265.179274</v>
       </c>
       <c r="G79" t="n">
-        <v>9822.015986</v>
+        <v>9362.496879</v>
       </c>
       <c r="H79" t="n">
-        <v>11322.478401</v>
+        <v>10950.357884</v>
       </c>
       <c r="I79" t="n">
-        <v>12227.826955</v>
+        <v>11920.647783</v>
       </c>
       <c r="J79" t="n">
-        <v>12651.418481</v>
+        <v>12381.933806</v>
       </c>
       <c r="K79" t="n">
-        <v>12669.258662</v>
+        <v>12420.828257</v>
       </c>
       <c r="L79" t="n">
-        <v>12345.711839</v>
+        <v>12109.745776</v>
       </c>
       <c r="M79" t="n">
-        <v>11830.62143</v>
+        <v>11604.604716</v>
       </c>
       <c r="N79" t="n">
-        <v>11149.528103</v>
+        <v>10935.292748</v>
       </c>
       <c r="O79" t="n">
-        <v>10407.140585</v>
+        <v>10207.677317</v>
       </c>
       <c r="P79" t="n">
-        <v>9670.345101000001</v>
+        <v>9487.849362000001</v>
       </c>
       <c r="Q79" t="n">
-        <v>9067.572034999999</v>
+        <v>8901.483018000001</v>
       </c>
       <c r="R79" t="n">
-        <v>8507.154082999999</v>
+        <v>8357.489903</v>
       </c>
       <c r="S79" t="n">
-        <v>8025.696935</v>
+        <v>7891.616376</v>
       </c>
       <c r="T79" t="n">
-        <v>7637.056395</v>
+        <v>7517.526322</v>
       </c>
       <c r="U79" t="n">
-        <v>7339.31963</v>
+        <v>7233.431059</v>
       </c>
       <c r="V79" t="n">
-        <v>7084.374313</v>
+        <v>6992.780937</v>
       </c>
     </row>
     <row r="80">
@@ -6454,58 +6454,58 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4220.189627</v>
+        <v>4032.772654</v>
       </c>
       <c r="F80" t="n">
-        <v>4777.284656</v>
+        <v>4471.260739</v>
       </c>
       <c r="G80" t="n">
-        <v>5472.273528</v>
+        <v>5048.079698</v>
       </c>
       <c r="H80" t="n">
-        <v>5954.822764</v>
+        <v>5450.624246</v>
       </c>
       <c r="I80" t="n">
-        <v>6368.921334</v>
+        <v>5816.548386</v>
       </c>
       <c r="J80" t="n">
-        <v>6775.577713</v>
+        <v>6198.315235</v>
       </c>
       <c r="K80" t="n">
-        <v>7098.698818</v>
+        <v>6520.583928</v>
       </c>
       <c r="L80" t="n">
-        <v>7253.220748</v>
+        <v>6695.874286</v>
       </c>
       <c r="M80" t="n">
-        <v>7243.924845</v>
+        <v>6721.183029</v>
       </c>
       <c r="N80" t="n">
-        <v>7063.941565</v>
+        <v>6584.632075</v>
       </c>
       <c r="O80" t="n">
-        <v>6785.956936</v>
+        <v>6352.147115</v>
       </c>
       <c r="P80" t="n">
-        <v>6468.705304</v>
+        <v>6078.578513</v>
       </c>
       <c r="Q80" t="n">
-        <v>6222.063102</v>
+        <v>5868.025424</v>
       </c>
       <c r="R80" t="n">
-        <v>5984.784732</v>
+        <v>5664.476287</v>
       </c>
       <c r="S80" t="n">
-        <v>5782.123257</v>
+        <v>5492.876276</v>
       </c>
       <c r="T80" t="n">
-        <v>5629.203614</v>
+        <v>5368.791285</v>
       </c>
       <c r="U80" t="n">
-        <v>5529.816364</v>
+        <v>5297.154111</v>
       </c>
       <c r="V80" t="n">
-        <v>5454.278583</v>
+        <v>5251.332215</v>
       </c>
     </row>
     <row r="81">
@@ -6530,58 +6530,58 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5709.623701</v>
+        <v>4867.200063</v>
       </c>
       <c r="F81" t="n">
-        <v>7215.405192</v>
+        <v>6255.613016</v>
       </c>
       <c r="G81" t="n">
-        <v>8455.275942</v>
+        <v>7444.277359</v>
       </c>
       <c r="H81" t="n">
-        <v>9297.324243999999</v>
+        <v>8283.790131</v>
       </c>
       <c r="I81" t="n">
-        <v>9923.408874999999</v>
+        <v>8915.214540999999</v>
       </c>
       <c r="J81" t="n">
-        <v>10413.119936</v>
+        <v>9408.459321</v>
       </c>
       <c r="K81" t="n">
-        <v>10695.176364</v>
+        <v>9705.273112999999</v>
       </c>
       <c r="L81" t="n">
-        <v>10710.352931</v>
+        <v>9755.158952</v>
       </c>
       <c r="M81" t="n">
-        <v>10525.101801</v>
+        <v>9619.637854000001</v>
       </c>
       <c r="N81" t="n">
-        <v>10132.394242</v>
+        <v>9291.93685</v>
       </c>
       <c r="O81" t="n">
-        <v>9647.909752</v>
+        <v>8877.965695000001</v>
       </c>
       <c r="P81" t="n">
-        <v>9141.477575999999</v>
+        <v>8442.305719</v>
       </c>
       <c r="Q81" t="n">
-        <v>8749.163417</v>
+        <v>8111.412688</v>
       </c>
       <c r="R81" t="n">
-        <v>8396.489325</v>
+        <v>7817.23567</v>
       </c>
       <c r="S81" t="n">
-        <v>8124.863165</v>
+        <v>7599.546577</v>
       </c>
       <c r="T81" t="n">
-        <v>7951.447985</v>
+        <v>7476.353328</v>
       </c>
       <c r="U81" t="n">
-        <v>7877.640049</v>
+        <v>7451.450009</v>
       </c>
       <c r="V81" t="n">
-        <v>7862.121707</v>
+        <v>7488.951344</v>
       </c>
     </row>
     <row r="82">
@@ -6606,58 +6606,58 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>14050.611557</v>
+        <v>14383.628898</v>
       </c>
       <c r="F82" t="n">
-        <v>15362.809287</v>
+        <v>15743.937255</v>
       </c>
       <c r="G82" t="n">
-        <v>17269.129663</v>
+        <v>17652.501835</v>
       </c>
       <c r="H82" t="n">
-        <v>18107.66924</v>
+        <v>18476.677688</v>
       </c>
       <c r="I82" t="n">
-        <v>18288.015993</v>
+        <v>18654.462205</v>
       </c>
       <c r="J82" t="n">
-        <v>18182.73929</v>
+        <v>18562.864934</v>
       </c>
       <c r="K82" t="n">
-        <v>17786.386441</v>
+        <v>18180.13092</v>
       </c>
       <c r="L82" t="n">
-        <v>17069.366744</v>
+        <v>17466.191976</v>
       </c>
       <c r="M82" t="n">
-        <v>16149.127879</v>
+        <v>16537.531268</v>
       </c>
       <c r="N82" t="n">
-        <v>15026.930146</v>
+        <v>15395.350746</v>
       </c>
       <c r="O82" t="n">
-        <v>13819.991927</v>
+        <v>14162.562244</v>
       </c>
       <c r="P82" t="n">
-        <v>12630.040818</v>
+        <v>12944.395266</v>
       </c>
       <c r="Q82" t="n">
-        <v>11638.668591</v>
+        <v>11927.879397</v>
       </c>
       <c r="R82" t="n">
-        <v>10728.172393</v>
+        <v>10991.905524</v>
       </c>
       <c r="S82" t="n">
-        <v>9933.157459</v>
+        <v>10172.577214</v>
       </c>
       <c r="T82" t="n">
-        <v>9261.072932999999</v>
+        <v>9477.34168</v>
       </c>
       <c r="U82" t="n">
-        <v>8690.432805</v>
+        <v>8883.92453</v>
       </c>
       <c r="V82" t="n">
-        <v>8159.96956</v>
+        <v>8328.517099000001</v>
       </c>
     </row>
     <row r="83">
@@ -6682,58 +6682,58 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>41100.369495</v>
+        <v>39353.399603</v>
       </c>
       <c r="F83" t="n">
-        <v>54137.410262</v>
+        <v>52829.945852</v>
       </c>
       <c r="G83" t="n">
-        <v>71051.70475400001</v>
+        <v>70650.55162499999</v>
       </c>
       <c r="H83" t="n">
-        <v>82910.943453</v>
+        <v>83372.86113400001</v>
       </c>
       <c r="I83" t="n">
-        <v>88461.003925</v>
+        <v>89496.053541</v>
       </c>
       <c r="J83" t="n">
-        <v>89484.776396</v>
+        <v>90795.246442</v>
       </c>
       <c r="K83" t="n">
-        <v>87582.91663000001</v>
+        <v>88951.28884199999</v>
       </c>
       <c r="L83" t="n">
-        <v>83665.679156</v>
+        <v>84976.88387600001</v>
       </c>
       <c r="M83" t="n">
-        <v>78798.133426</v>
+        <v>80011.376181</v>
       </c>
       <c r="N83" t="n">
-        <v>73070.864149</v>
+        <v>74171.12786399999</v>
       </c>
       <c r="O83" t="n">
-        <v>67116.715385</v>
+        <v>68105.564354</v>
       </c>
       <c r="P83" t="n">
-        <v>61358.877143</v>
+        <v>62246.504055</v>
       </c>
       <c r="Q83" t="n">
-        <v>56661.631988</v>
+        <v>57467.844546</v>
       </c>
       <c r="R83" t="n">
-        <v>52348.928134</v>
+        <v>53081.971355</v>
       </c>
       <c r="S83" t="n">
-        <v>48579.723595</v>
+        <v>49245.355013</v>
       </c>
       <c r="T83" t="n">
-        <v>45451.796661</v>
+        <v>46052.518139</v>
       </c>
       <c r="U83" t="n">
-        <v>42879.287781</v>
+        <v>43415.194426</v>
       </c>
       <c r="V83" t="n">
-        <v>40576.719253</v>
+        <v>41041.822263</v>
       </c>
     </row>
     <row r="84">
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10859.383573</v>
+        <v>10750.124364</v>
       </c>
       <c r="F86" t="n">
-        <v>10887.534424</v>
+        <v>10773.93266</v>
       </c>
       <c r="G86" t="n">
-        <v>11521.709004</v>
+        <v>11403.730312</v>
       </c>
       <c r="H86" t="n">
-        <v>11735.407323</v>
+        <v>11617.898381</v>
       </c>
       <c r="I86" t="n">
-        <v>11687.745867</v>
+        <v>11573.852661</v>
       </c>
       <c r="J86" t="n">
-        <v>11925.309592</v>
+        <v>11812.987454</v>
       </c>
       <c r="K86" t="n">
-        <v>11798.848901</v>
+        <v>11692.13697</v>
       </c>
       <c r="L86" t="n">
-        <v>11386.015312</v>
+        <v>11287.894353</v>
       </c>
       <c r="M86" t="n">
-        <v>10733.051102</v>
+        <v>10644.561134</v>
       </c>
       <c r="N86" t="n">
-        <v>9964.243397</v>
+        <v>9884.106635</v>
       </c>
       <c r="O86" t="n">
-        <v>9285.900320999999</v>
+        <v>9211.453487000001</v>
       </c>
       <c r="P86" t="n">
-        <v>8577.037340999999</v>
+        <v>8507.330426</v>
       </c>
       <c r="Q86" t="n">
-        <v>7969.058052</v>
+        <v>7904.269484</v>
       </c>
       <c r="R86" t="n">
-        <v>7395.267932</v>
+        <v>7336.965968</v>
       </c>
       <c r="S86" t="n">
-        <v>6892.72318</v>
+        <v>6841.867338</v>
       </c>
       <c r="T86" t="n">
-        <v>6472.495995</v>
+        <v>6429.107432</v>
       </c>
       <c r="U86" t="n">
-        <v>6100.64548</v>
+        <v>6064.474555</v>
       </c>
       <c r="V86" t="n">
-        <v>5734.178693</v>
+        <v>5705.077077</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1615.506382</v>
+        <v>1607.106862</v>
       </c>
       <c r="F87" t="n">
-        <v>1762.471459</v>
+        <v>1757.132743</v>
       </c>
       <c r="G87" t="n">
-        <v>2029.198035</v>
+        <v>2031.426137</v>
       </c>
       <c r="H87" t="n">
-        <v>2208.466814</v>
+        <v>2217.620542</v>
       </c>
       <c r="I87" t="n">
-        <v>2317.306153</v>
+        <v>2331.204373</v>
       </c>
       <c r="J87" t="n">
-        <v>2469.833207</v>
+        <v>2487.094319</v>
       </c>
       <c r="K87" t="n">
-        <v>2539.990075</v>
+        <v>2558.745863</v>
       </c>
       <c r="L87" t="n">
-        <v>2537.807068</v>
+        <v>2556.74147</v>
       </c>
       <c r="M87" t="n">
-        <v>2466.31611</v>
+        <v>2484.404294</v>
       </c>
       <c r="N87" t="n">
-        <v>2349.564738</v>
+        <v>2366.073623</v>
       </c>
       <c r="O87" t="n">
-        <v>2235.595558</v>
+        <v>2250.363004</v>
       </c>
       <c r="P87" t="n">
-        <v>2096.742538</v>
+        <v>2109.479656</v>
       </c>
       <c r="Q87" t="n">
-        <v>1968.53019</v>
+        <v>1979.284983</v>
       </c>
       <c r="R87" t="n">
-        <v>1838.254785</v>
+        <v>1847.141285</v>
       </c>
       <c r="S87" t="n">
-        <v>1718.185234</v>
+        <v>1725.429659</v>
       </c>
       <c r="T87" t="n">
-        <v>1614.15789</v>
+        <v>1619.943233</v>
       </c>
       <c r="U87" t="n">
-        <v>1519.99501</v>
+        <v>1524.465028</v>
       </c>
       <c r="V87" t="n">
-        <v>1426.582388</v>
+        <v>1429.847246</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>21315.843702</v>
+        <v>21664.896701</v>
       </c>
       <c r="F88" t="n">
-        <v>19103.037233</v>
+        <v>19326.988198</v>
       </c>
       <c r="G88" t="n">
-        <v>19472.238699</v>
+        <v>19564.585124</v>
       </c>
       <c r="H88" t="n">
-        <v>19840.809807</v>
+        <v>19851.510871</v>
       </c>
       <c r="I88" t="n">
-        <v>20026.637456</v>
+        <v>20002.916641</v>
       </c>
       <c r="J88" t="n">
-        <v>20804.17239</v>
+        <v>20772.630128</v>
       </c>
       <c r="K88" t="n">
-        <v>21006.63091</v>
+        <v>20977.704152</v>
       </c>
       <c r="L88" t="n">
-        <v>20691.542673</v>
+        <v>20667.222336</v>
       </c>
       <c r="M88" t="n">
-        <v>19868.13668</v>
+        <v>19849.104116</v>
       </c>
       <c r="N88" t="n">
-        <v>18717.826445</v>
+        <v>18704.826671</v>
       </c>
       <c r="O88" t="n">
-        <v>17629.456118</v>
+        <v>17622.767285</v>
       </c>
       <c r="P88" t="n">
-        <v>16398.306153</v>
+        <v>16396.78331</v>
       </c>
       <c r="Q88" t="n">
-        <v>15319.195122</v>
+        <v>15321.110818</v>
       </c>
       <c r="R88" t="n">
-        <v>14298.888723</v>
+        <v>14302.850835</v>
       </c>
       <c r="S88" t="n">
-        <v>13417.656982</v>
+        <v>13422.61548</v>
       </c>
       <c r="T88" t="n">
-        <v>12685.570627</v>
+        <v>12691.251726</v>
       </c>
       <c r="U88" t="n">
-        <v>12032.451517</v>
+        <v>12038.58963</v>
       </c>
       <c r="V88" t="n">
-        <v>11373.525626</v>
+        <v>11379.573986</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5267.442511</v>
+        <v>5458.938057</v>
       </c>
       <c r="F89" t="n">
-        <v>4441.680472</v>
+        <v>4642.809841</v>
       </c>
       <c r="G89" t="n">
-        <v>4318.479059</v>
+        <v>4530.852463</v>
       </c>
       <c r="H89" t="n">
-        <v>4123.558026</v>
+        <v>4333.940437</v>
       </c>
       <c r="I89" t="n">
-        <v>3891.178862</v>
+        <v>4091.702051</v>
       </c>
       <c r="J89" t="n">
-        <v>3794.450376</v>
+        <v>3987.703595</v>
       </c>
       <c r="K89" t="n">
-        <v>3615.898051</v>
+        <v>3795.209117</v>
       </c>
       <c r="L89" t="n">
-        <v>3378.476456</v>
+        <v>3540.159284</v>
       </c>
       <c r="M89" t="n">
-        <v>3097.074766</v>
+        <v>3239.904657</v>
       </c>
       <c r="N89" t="n">
-        <v>2806.861261</v>
+        <v>2931.898877</v>
       </c>
       <c r="O89" t="n">
-        <v>2565.808749</v>
+        <v>2676.492587</v>
       </c>
       <c r="P89" t="n">
-        <v>2332.005571</v>
+        <v>2429.405126</v>
       </c>
       <c r="Q89" t="n">
-        <v>2135.684444</v>
+        <v>2221.810104</v>
       </c>
       <c r="R89" t="n">
-        <v>1954.298278</v>
+        <v>2030.018869</v>
       </c>
       <c r="S89" t="n">
-        <v>1794.996144</v>
+        <v>1861.322133</v>
       </c>
       <c r="T89" t="n">
-        <v>1658.907377</v>
+        <v>1716.643336</v>
       </c>
       <c r="U89" t="n">
-        <v>1536.464376</v>
+        <v>1585.799057</v>
       </c>
       <c r="V89" t="n">
-        <v>1416.026841</v>
+        <v>1456.620101</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>13443.703044</v>
+        <v>13314.226515</v>
       </c>
       <c r="F90" t="n">
-        <v>13455.076137</v>
+        <v>13280.101296</v>
       </c>
       <c r="G90" t="n">
-        <v>14487.72547</v>
+        <v>14308.511779</v>
       </c>
       <c r="H90" t="n">
-        <v>14967.101689</v>
+        <v>14805.353498</v>
       </c>
       <c r="I90" t="n">
-        <v>15020.062219</v>
+        <v>14880.369417</v>
       </c>
       <c r="J90" t="n">
-        <v>15359.010334</v>
+        <v>15233.420972</v>
       </c>
       <c r="K90" t="n">
-        <v>15182.495357</v>
+        <v>15071.225209</v>
       </c>
       <c r="L90" t="n">
-        <v>14611.992677</v>
+        <v>14516.125706</v>
       </c>
       <c r="M90" t="n">
-        <v>13715.245365</v>
+        <v>13635.645167</v>
       </c>
       <c r="N90" t="n">
-        <v>12651.853241</v>
+        <v>12586.754316</v>
       </c>
       <c r="O90" t="n">
-        <v>11700.478688</v>
+        <v>11646.350575</v>
       </c>
       <c r="P90" t="n">
-        <v>10708.557436</v>
+        <v>10663.362355</v>
       </c>
       <c r="Q90" t="n">
-        <v>9855.946043</v>
+        <v>9817.86018</v>
       </c>
       <c r="R90" t="n">
-        <v>9071.468822999999</v>
+        <v>9039.661617</v>
       </c>
       <c r="S90" t="n">
-        <v>8399.327417</v>
+        <v>8373.106269</v>
       </c>
       <c r="T90" t="n">
-        <v>7845.156187</v>
+        <v>7823.780054</v>
       </c>
       <c r="U90" t="n">
-        <v>7364.306032</v>
+        <v>7347.055421</v>
       </c>
       <c r="V90" t="n">
-        <v>6902.96865</v>
+        <v>6889.32609</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5486.806221</v>
+        <v>5501.855055</v>
       </c>
       <c r="F91" t="n">
-        <v>5318.064336</v>
+        <v>5337.002442</v>
       </c>
       <c r="G91" t="n">
-        <v>5538.789988</v>
+        <v>5562.610497</v>
       </c>
       <c r="H91" t="n">
-        <v>5526.299883</v>
+        <v>5547.692126</v>
       </c>
       <c r="I91" t="n">
-        <v>5368.455284</v>
+        <v>5382.656685</v>
       </c>
       <c r="J91" t="n">
-        <v>5340.290112</v>
+        <v>5345.973699</v>
       </c>
       <c r="K91" t="n">
-        <v>5163.799309</v>
+        <v>5161.385266</v>
       </c>
       <c r="L91" t="n">
-        <v>4879.209919</v>
+        <v>4871.041875</v>
       </c>
       <c r="M91" t="n">
-        <v>4502.856284</v>
+        <v>4491.395884</v>
       </c>
       <c r="N91" t="n">
-        <v>4085.841985</v>
+        <v>4073.68125</v>
       </c>
       <c r="O91" t="n">
-        <v>3727.991044</v>
+        <v>3716.563368</v>
       </c>
       <c r="P91" t="n">
-        <v>3376.524124</v>
+        <v>3366.750326</v>
       </c>
       <c r="Q91" t="n">
-        <v>3084.986452</v>
+        <v>3076.981746</v>
       </c>
       <c r="R91" t="n">
-        <v>2824.785036</v>
+        <v>2818.50882</v>
       </c>
       <c r="S91" t="n">
-        <v>2606.76986</v>
+        <v>2602.113926</v>
       </c>
       <c r="T91" t="n">
-        <v>2431.69627</v>
+        <v>2428.484874</v>
       </c>
       <c r="U91" t="n">
-        <v>2285.331594</v>
+        <v>2283.334993</v>
       </c>
       <c r="V91" t="n">
-        <v>2150.653265</v>
+        <v>2149.590523</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2062.619571</v>
+        <v>1966.559988</v>
       </c>
       <c r="F92" t="n">
-        <v>2286.301272</v>
+        <v>2180.719641</v>
       </c>
       <c r="G92" t="n">
-        <v>2548.892764</v>
+        <v>2442.226649</v>
       </c>
       <c r="H92" t="n">
-        <v>2677.961952</v>
+        <v>2574.964344</v>
       </c>
       <c r="I92" t="n">
-        <v>2722.688738</v>
+        <v>2624.799278</v>
       </c>
       <c r="J92" t="n">
-        <v>2821.324508</v>
+        <v>2725.529825</v>
       </c>
       <c r="K92" t="n">
-        <v>2822.076127</v>
+        <v>2731.301487</v>
       </c>
       <c r="L92" t="n">
-        <v>2743.62094</v>
+        <v>2660.052456</v>
       </c>
       <c r="M92" t="n">
-        <v>2596.631192</v>
+        <v>2522.017238</v>
       </c>
       <c r="N92" t="n">
-        <v>2411.994422</v>
+        <v>2346.804141</v>
       </c>
       <c r="O92" t="n">
-        <v>2244.256447</v>
+        <v>2187.335861</v>
       </c>
       <c r="P92" t="n">
-        <v>2065.635939</v>
+        <v>2016.695422</v>
       </c>
       <c r="Q92" t="n">
-        <v>1909.881222</v>
+        <v>1867.956295</v>
       </c>
       <c r="R92" t="n">
-        <v>1763.36259</v>
+        <v>1727.910845</v>
       </c>
       <c r="S92" t="n">
-        <v>1637.249173</v>
+        <v>1607.534722</v>
       </c>
       <c r="T92" t="n">
-        <v>1535.309523</v>
+        <v>1510.576582</v>
       </c>
       <c r="U92" t="n">
-        <v>1449.578406</v>
+        <v>1429.302226</v>
       </c>
       <c r="V92" t="n">
-        <v>1368.194861</v>
+        <v>1352.132464</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>242.742707</v>
+        <v>220.254723</v>
       </c>
       <c r="F93" t="n">
-        <v>315.299461</v>
+        <v>289.072542</v>
       </c>
       <c r="G93" t="n">
-        <v>380.717535</v>
+        <v>352.557943</v>
       </c>
       <c r="H93" t="n">
-        <v>422.500214</v>
+        <v>394.648676</v>
       </c>
       <c r="I93" t="n">
-        <v>446.782372</v>
+        <v>420.388071</v>
       </c>
       <c r="J93" t="n">
-        <v>476.215663</v>
+        <v>450.790618</v>
       </c>
       <c r="K93" t="n">
-        <v>487.867007</v>
+        <v>464.106866</v>
       </c>
       <c r="L93" t="n">
-        <v>485.602481</v>
+        <v>463.892026</v>
       </c>
       <c r="M93" t="n">
-        <v>471.2627</v>
+        <v>451.8063</v>
       </c>
       <c r="N93" t="n">
-        <v>449.462992</v>
+        <v>432.230613</v>
       </c>
       <c r="O93" t="n">
-        <v>429.242064</v>
+        <v>413.899005</v>
       </c>
       <c r="P93" t="n">
-        <v>404.751989</v>
+        <v>391.272748</v>
       </c>
       <c r="Q93" t="n">
-        <v>382.402725</v>
+        <v>370.601973</v>
       </c>
       <c r="R93" t="n">
-        <v>359.855476</v>
+        <v>349.662733</v>
       </c>
       <c r="S93" t="n">
-        <v>339.819093</v>
+        <v>331.098295</v>
       </c>
       <c r="T93" t="n">
-        <v>323.438984</v>
+        <v>316.040931</v>
       </c>
       <c r="U93" t="n">
-        <v>309.588548</v>
+        <v>303.41709</v>
       </c>
       <c r="V93" t="n">
-        <v>296.257572</v>
+        <v>291.284193</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>57288.677037</v>
+        <v>57194.219176</v>
       </c>
       <c r="F94" t="n">
-        <v>58337.379926</v>
+        <v>58386.639966</v>
       </c>
       <c r="G94" t="n">
-        <v>62233.257366</v>
+        <v>62367.419689</v>
       </c>
       <c r="H94" t="n">
-        <v>63289.900177</v>
+        <v>63438.341509</v>
       </c>
       <c r="I94" t="n">
-        <v>62474.704332</v>
+        <v>62594.560673</v>
       </c>
       <c r="J94" t="n">
-        <v>62989.185107</v>
+        <v>63074.940534</v>
       </c>
       <c r="K94" t="n">
-        <v>61584.189844</v>
+        <v>61637.934945</v>
       </c>
       <c r="L94" t="n">
-        <v>58776.45003</v>
+        <v>58804.152276</v>
       </c>
       <c r="M94" t="n">
-        <v>54786.397695</v>
+        <v>54792.135852</v>
       </c>
       <c r="N94" t="n">
-        <v>50196.155307</v>
+        <v>50184.988943</v>
       </c>
       <c r="O94" t="n">
-        <v>46112.245793</v>
+        <v>46089.375539</v>
       </c>
       <c r="P94" t="n">
-        <v>41896.13933</v>
+        <v>41866.841175</v>
       </c>
       <c r="Q94" t="n">
-        <v>38266.018311</v>
+        <v>38232.68305</v>
       </c>
       <c r="R94" t="n">
-        <v>34968.288733</v>
+        <v>34931.435167</v>
       </c>
       <c r="S94" t="n">
-        <v>32202.448381</v>
+        <v>32162.373343</v>
       </c>
       <c r="T94" t="n">
-        <v>29987.555815</v>
+        <v>29945.384332</v>
       </c>
       <c r="U94" t="n">
-        <v>28126.40774</v>
+        <v>28084.67231</v>
       </c>
       <c r="V94" t="n">
-        <v>26384.268143</v>
+        <v>26345.991749</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>29534.378664</v>
+        <v>29033.750503</v>
       </c>
       <c r="F95" t="n">
-        <v>31097.434659</v>
+        <v>30670.937851</v>
       </c>
       <c r="G95" t="n">
-        <v>33751.847973</v>
+        <v>33446.118129</v>
       </c>
       <c r="H95" t="n">
-        <v>34652.915293</v>
+        <v>34457.455107</v>
       </c>
       <c r="I95" t="n">
-        <v>34402.688283</v>
+        <v>34289.167443</v>
       </c>
       <c r="J95" t="n">
-        <v>34693.241179</v>
+        <v>34628.873895</v>
       </c>
       <c r="K95" t="n">
-        <v>33711.279427</v>
+        <v>33679.449799</v>
       </c>
       <c r="L95" t="n">
-        <v>31777.143613</v>
+        <v>31766.57578</v>
       </c>
       <c r="M95" t="n">
-        <v>29116.777308</v>
+        <v>29121.06565</v>
       </c>
       <c r="N95" t="n">
-        <v>26145.687461</v>
+        <v>26159.497557</v>
       </c>
       <c r="O95" t="n">
-        <v>23528.231545</v>
+        <v>23547.131098</v>
       </c>
       <c r="P95" t="n">
-        <v>20964.772889</v>
+        <v>20986.083578</v>
       </c>
       <c r="Q95" t="n">
-        <v>18803.909598</v>
+        <v>18826.320906</v>
       </c>
       <c r="R95" t="n">
-        <v>16885.712349</v>
+        <v>16908.622577</v>
       </c>
       <c r="S95" t="n">
-        <v>15283.286141</v>
+        <v>15306.299477</v>
       </c>
       <c r="T95" t="n">
-        <v>13992.888796</v>
+        <v>14015.379608</v>
       </c>
       <c r="U95" t="n">
-        <v>12907.625693</v>
+        <v>12928.544424</v>
       </c>
       <c r="V95" t="n">
-        <v>11908.888243</v>
+        <v>11927.298563</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>14671.911802</v>
+        <v>15065.813246</v>
       </c>
       <c r="F96" t="n">
-        <v>12832.379636</v>
+        <v>13210.125868</v>
       </c>
       <c r="G96" t="n">
-        <v>12508.909601</v>
+        <v>12827.650473</v>
       </c>
       <c r="H96" t="n">
-        <v>12213.442292</v>
+        <v>12479.476788</v>
       </c>
       <c r="I96" t="n">
-        <v>11879.513329</v>
+        <v>12111.229716</v>
       </c>
       <c r="J96" t="n">
-        <v>11942.772064</v>
+        <v>12162.405744</v>
       </c>
       <c r="K96" t="n">
-        <v>11692.74789</v>
+        <v>11900.783618</v>
       </c>
       <c r="L96" t="n">
-        <v>11183.303334</v>
+        <v>11377.056064</v>
       </c>
       <c r="M96" t="n">
-        <v>10443.7452</v>
+        <v>10619.565805</v>
       </c>
       <c r="N96" t="n">
-        <v>9584.340225</v>
+        <v>9741.080414</v>
       </c>
       <c r="O96" t="n">
-        <v>8810.711243</v>
+        <v>8950.99927</v>
       </c>
       <c r="P96" t="n">
-        <v>8006.139963</v>
+        <v>8130.209943</v>
       </c>
       <c r="Q96" t="n">
-        <v>7308.928471</v>
+        <v>7418.603738</v>
       </c>
       <c r="R96" t="n">
-        <v>6667.887397</v>
+        <v>6763.732496</v>
       </c>
       <c r="S96" t="n">
-        <v>6117.581131</v>
+        <v>6200.517227</v>
       </c>
       <c r="T96" t="n">
-        <v>5660.816602</v>
+        <v>5731.816237</v>
       </c>
       <c r="U96" t="n">
-        <v>5260.646482</v>
+        <v>5320.280702</v>
       </c>
       <c r="V96" t="n">
-        <v>4875.756288</v>
+        <v>4924.07351</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3124.723967</v>
+        <v>3135.993988</v>
       </c>
       <c r="F97" t="n">
-        <v>2914.013379</v>
+        <v>2895.209344</v>
       </c>
       <c r="G97" t="n">
-        <v>3072.499194</v>
+        <v>3026.575493</v>
       </c>
       <c r="H97" t="n">
-        <v>3212.386281</v>
+        <v>3151.847471</v>
       </c>
       <c r="I97" t="n">
-        <v>3308.517867</v>
+        <v>3243.433755</v>
       </c>
       <c r="J97" t="n">
-        <v>3489.231944</v>
+        <v>3422.685694</v>
       </c>
       <c r="K97" t="n">
-        <v>3559.029328</v>
+        <v>3494.868936</v>
       </c>
       <c r="L97" t="n">
-        <v>3530.950615</v>
+        <v>3471.201493</v>
       </c>
       <c r="M97" t="n">
-        <v>3412.728651</v>
+        <v>3358.616956</v>
       </c>
       <c r="N97" t="n">
-        <v>3240.715669</v>
+        <v>3192.604104</v>
       </c>
       <c r="O97" t="n">
-        <v>3085.613706</v>
+        <v>3042.800198</v>
       </c>
       <c r="P97" t="n">
-        <v>2909.718674</v>
+        <v>2872.117882</v>
       </c>
       <c r="Q97" t="n">
-        <v>2758.514915</v>
+        <v>2725.572266</v>
       </c>
       <c r="R97" t="n">
-        <v>2610.206101</v>
+        <v>2581.765012</v>
       </c>
       <c r="S97" t="n">
-        <v>2477.812491</v>
+        <v>2453.577359</v>
       </c>
       <c r="T97" t="n">
-        <v>2366.460969</v>
+        <v>2346.046689</v>
       </c>
       <c r="U97" t="n">
-        <v>2266.604736</v>
+        <v>2249.710176</v>
       </c>
       <c r="V97" t="n">
-        <v>2164.003038</v>
+        <v>2150.488103</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>18783.330617</v>
+        <v>19061.896436</v>
       </c>
       <c r="F98" t="n">
-        <v>16477.449483</v>
+        <v>16658.590227</v>
       </c>
       <c r="G98" t="n">
-        <v>16849.313567</v>
+        <v>16960.272051</v>
       </c>
       <c r="H98" t="n">
-        <v>17106.443682</v>
+        <v>17166.934315</v>
       </c>
       <c r="I98" t="n">
-        <v>17050.840363</v>
+        <v>17078.305064</v>
       </c>
       <c r="J98" t="n">
-        <v>17903.26587</v>
+        <v>17911.912327</v>
       </c>
       <c r="K98" t="n">
-        <v>19251.041759</v>
+        <v>19247.967739</v>
       </c>
       <c r="L98" t="n">
-        <v>19561.463222</v>
+        <v>19551.674538</v>
       </c>
       <c r="M98" t="n">
-        <v>19111.283673</v>
+        <v>19098.426298</v>
       </c>
       <c r="N98" t="n">
-        <v>18083.374176</v>
+        <v>18069.83137</v>
       </c>
       <c r="O98" t="n">
-        <v>16965.415153</v>
+        <v>16952.398358</v>
       </c>
       <c r="P98" t="n">
-        <v>15562.195944</v>
+        <v>15550.476985</v>
       </c>
       <c r="Q98" t="n">
-        <v>14365.984822</v>
+        <v>14355.659991</v>
       </c>
       <c r="R98" t="n">
-        <v>13254.827217</v>
+        <v>13245.972114</v>
       </c>
       <c r="S98" t="n">
-        <v>12319.717574</v>
+        <v>12312.227398</v>
       </c>
       <c r="T98" t="n">
-        <v>11527.839274</v>
+        <v>11521.514954</v>
       </c>
       <c r="U98" t="n">
-        <v>10830.220312</v>
+        <v>10825.021944</v>
       </c>
       <c r="V98" t="n">
-        <v>10169.673134</v>
+        <v>10165.607576</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>26757.547471</v>
+        <v>27274.937835</v>
       </c>
       <c r="F99" t="n">
-        <v>23655.619623</v>
+        <v>24154.558958</v>
       </c>
       <c r="G99" t="n">
-        <v>23991.61299</v>
+        <v>24514.195869</v>
       </c>
       <c r="H99" t="n">
-        <v>23918.520107</v>
+        <v>24439.913202</v>
       </c>
       <c r="I99" t="n">
-        <v>23382.517309</v>
+        <v>23879.94516</v>
       </c>
       <c r="J99" t="n">
-        <v>24131.47661</v>
+        <v>24622.963218</v>
       </c>
       <c r="K99" t="n">
-        <v>25561.392221</v>
+        <v>26053.365892</v>
       </c>
       <c r="L99" t="n">
-        <v>25670.130598</v>
+        <v>26133.086424</v>
       </c>
       <c r="M99" t="n">
-        <v>24883.310033</v>
+        <v>25301.736518</v>
       </c>
       <c r="N99" t="n">
-        <v>23451.453852</v>
+        <v>23818.037966</v>
       </c>
       <c r="O99" t="n">
-        <v>21992.404214</v>
+        <v>22311.260546</v>
       </c>
       <c r="P99" t="n">
-        <v>20203.676254</v>
+        <v>20474.245154</v>
       </c>
       <c r="Q99" t="n">
-        <v>18695.618019</v>
+        <v>18925.498716</v>
       </c>
       <c r="R99" t="n">
-        <v>17305.647782</v>
+        <v>17499.45497</v>
       </c>
       <c r="S99" t="n">
-        <v>16145.725224</v>
+        <v>16308.635569</v>
       </c>
       <c r="T99" t="n">
-        <v>15165.609024</v>
+        <v>15301.28842</v>
       </c>
       <c r="U99" t="n">
-        <v>14307.789359</v>
+        <v>14418.694254</v>
       </c>
       <c r="V99" t="n">
-        <v>13482.641058</v>
+        <v>13570.139974</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>8985.511318999999</v>
+        <v>8923.985854</v>
       </c>
       <c r="F100" t="n">
-        <v>9082.052862</v>
+        <v>9006.926171999999</v>
       </c>
       <c r="G100" t="n">
-        <v>10005.864902</v>
+        <v>9913.848480000001</v>
       </c>
       <c r="H100" t="n">
-        <v>10642.387463</v>
+        <v>10540.078223</v>
       </c>
       <c r="I100" t="n">
-        <v>10964.157481</v>
+        <v>10858.28216</v>
       </c>
       <c r="J100" t="n">
-        <v>11812.649221</v>
+        <v>11701.305156</v>
       </c>
       <c r="K100" t="n">
-        <v>12987.642333</v>
+        <v>12870.410865</v>
       </c>
       <c r="L100" t="n">
-        <v>13498.231871</v>
+        <v>13382.97052</v>
       </c>
       <c r="M100" t="n">
-        <v>13520.079092</v>
+        <v>13411.650266</v>
       </c>
       <c r="N100" t="n">
-        <v>13143.881087</v>
+        <v>13045.44506</v>
       </c>
       <c r="O100" t="n">
-        <v>12694.699259</v>
+        <v>12606.409407</v>
       </c>
       <c r="P100" t="n">
-        <v>11989.153766</v>
+        <v>11912.369649</v>
       </c>
       <c r="Q100" t="n">
-        <v>11389.425755</v>
+        <v>11322.909275</v>
       </c>
       <c r="R100" t="n">
-        <v>10818.02328</v>
+        <v>10760.991279</v>
       </c>
       <c r="S100" t="n">
-        <v>10359.465644</v>
+        <v>10310.763488</v>
       </c>
       <c r="T100" t="n">
-        <v>9995.061154000001</v>
+        <v>9953.825423</v>
       </c>
       <c r="U100" t="n">
-        <v>9698.422229</v>
+        <v>9664.142296</v>
       </c>
       <c r="V100" t="n">
-        <v>9432.085316999999</v>
+        <v>9404.532402999999</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>12337.576393</v>
+        <v>12503.503725</v>
       </c>
       <c r="F101" t="n">
-        <v>11063.985601</v>
+        <v>11194.522538</v>
       </c>
       <c r="G101" t="n">
-        <v>11354.983805</v>
+        <v>11465.4638</v>
       </c>
       <c r="H101" t="n">
-        <v>11468.324849</v>
+        <v>11560.330101</v>
       </c>
       <c r="I101" t="n">
-        <v>11354.519071</v>
+        <v>11430.105964</v>
       </c>
       <c r="J101" t="n">
-        <v>11862.961847</v>
+        <v>11929.342285</v>
       </c>
       <c r="K101" t="n">
-        <v>12736.025131</v>
+        <v>12796.589056</v>
       </c>
       <c r="L101" t="n">
-        <v>12989.459935</v>
+        <v>13042.353184</v>
       </c>
       <c r="M101" t="n">
-        <v>12810.927316</v>
+        <v>12855.854989</v>
       </c>
       <c r="N101" t="n">
-        <v>12291.129463</v>
+        <v>12328.707042</v>
       </c>
       <c r="O101" t="n">
-        <v>11735.559482</v>
+        <v>11767.315525</v>
       </c>
       <c r="P101" t="n">
-        <v>10971.483327</v>
+        <v>10998.137003</v>
       </c>
       <c r="Q101" t="n">
-        <v>10329.520816</v>
+        <v>10352.176178</v>
       </c>
       <c r="R101" t="n">
-        <v>9729.097983</v>
+        <v>9748.2827</v>
       </c>
       <c r="S101" t="n">
-        <v>9244.322097</v>
+        <v>9260.458884</v>
       </c>
       <c r="T101" t="n">
-        <v>8852.951381999999</v>
+        <v>8866.336901000001</v>
       </c>
       <c r="U101" t="n">
-        <v>8522.554835000001</v>
+        <v>8533.472068999999</v>
       </c>
       <c r="V101" t="n">
-        <v>8208.332105</v>
+        <v>8216.957806</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103395.697554</v>
+        <v>102717.80822</v>
       </c>
       <c r="F102" t="n">
-        <v>103749.09805</v>
+        <v>103279.656726</v>
       </c>
       <c r="G102" t="n">
-        <v>111093.348127</v>
+        <v>110755.639656</v>
       </c>
       <c r="H102" t="n">
-        <v>114666.475682</v>
+        <v>114423.427821</v>
       </c>
       <c r="I102" t="n">
-        <v>115269.809761</v>
+        <v>115089.63055</v>
       </c>
       <c r="J102" t="n">
-        <v>121920.809305</v>
+        <v>121770.720948</v>
       </c>
       <c r="K102" t="n">
-        <v>132043.039855</v>
+        <v>131906.621877</v>
       </c>
       <c r="L102" t="n">
-        <v>135321.989148</v>
+        <v>135198.566512</v>
       </c>
       <c r="M102" t="n">
-        <v>133734.653502</v>
+        <v>133621.136682</v>
       </c>
       <c r="N102" t="n">
-        <v>128441.180843</v>
+        <v>128335.984897</v>
       </c>
       <c r="O102" t="n">
-        <v>122774.087612</v>
+        <v>122675.433643</v>
       </c>
       <c r="P102" t="n">
-        <v>114973.603723</v>
+        <v>114883.968433</v>
       </c>
       <c r="Q102" t="n">
-        <v>108446.286562</v>
+        <v>108365.896097</v>
       </c>
       <c r="R102" t="n">
-        <v>102313.224604</v>
+        <v>102242.331453</v>
       </c>
       <c r="S102" t="n">
-        <v>97296.490745</v>
+        <v>97234.668147</v>
       </c>
       <c r="T102" t="n">
-        <v>93019.683586</v>
+        <v>92966.876276</v>
       </c>
       <c r="U102" t="n">
-        <v>89340.378495</v>
+        <v>89295.88052200001</v>
       </c>
       <c r="V102" t="n">
-        <v>85956.808581</v>
+        <v>85920.15534500001</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>165957.851649</v>
+        <v>167113.216481</v>
       </c>
       <c r="F103" t="n">
-        <v>150240.701365</v>
+        <v>150672.035229</v>
       </c>
       <c r="G103" t="n">
-        <v>155501.213919</v>
+        <v>155393.851247</v>
       </c>
       <c r="H103" t="n">
-        <v>158129.127782</v>
+        <v>157686.210828</v>
       </c>
       <c r="I103" t="n">
-        <v>156917.822149</v>
+        <v>156308.57174</v>
       </c>
       <c r="J103" t="n">
-        <v>163396.72581</v>
+        <v>162692.651569</v>
       </c>
       <c r="K103" t="n">
-        <v>173685.134551</v>
+        <v>172930.768252</v>
       </c>
       <c r="L103" t="n">
-        <v>174219.693422</v>
+        <v>173493.87128</v>
       </c>
       <c r="M103" t="n">
-        <v>168082.571145</v>
+        <v>167427.235189</v>
       </c>
       <c r="N103" t="n">
-        <v>157400.915494</v>
+        <v>156833.301596</v>
       </c>
       <c r="O103" t="n">
-        <v>146534.958498</v>
+        <v>146050.825749</v>
       </c>
       <c r="P103" t="n">
-        <v>133652.309316</v>
+        <v>133252.402185</v>
       </c>
       <c r="Q103" t="n">
-        <v>122781.223458</v>
+        <v>122453.219128</v>
       </c>
       <c r="R103" t="n">
-        <v>112778.713836</v>
+        <v>112514.002291</v>
       </c>
       <c r="S103" t="n">
-        <v>104406.582743</v>
+        <v>104194.2795</v>
       </c>
       <c r="T103" t="n">
-        <v>97410.78827800001</v>
+        <v>97241.309291</v>
       </c>
       <c r="U103" t="n">
-        <v>91448.973602</v>
+        <v>91315.521647</v>
       </c>
       <c r="V103" t="n">
-        <v>85776.953001</v>
+        <v>85676.46870500001</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>19166.183979</v>
+        <v>19042.420497</v>
       </c>
       <c r="F104" t="n">
-        <v>18647.70961</v>
+        <v>18561.783399</v>
       </c>
       <c r="G104" t="n">
-        <v>19402.009082</v>
+        <v>19336.104337</v>
       </c>
       <c r="H104" t="n">
-        <v>19458.837657</v>
+        <v>19413.478529</v>
       </c>
       <c r="I104" t="n">
-        <v>19024.804129</v>
+        <v>18996.481598</v>
       </c>
       <c r="J104" t="n">
-        <v>19587.726406</v>
+        <v>19571.247682</v>
       </c>
       <c r="K104" t="n">
-        <v>20663.018595</v>
+        <v>20655.300131</v>
       </c>
       <c r="L104" t="n">
-        <v>20614.777615</v>
+        <v>20613.623467</v>
       </c>
       <c r="M104" t="n">
-        <v>19808.499719</v>
+        <v>19811.264168</v>
       </c>
       <c r="N104" t="n">
-        <v>18482.52828</v>
+        <v>18486.963314</v>
       </c>
       <c r="O104" t="n">
-        <v>17142.470294</v>
+        <v>17147.162003</v>
       </c>
       <c r="P104" t="n">
-        <v>15573.729184</v>
+        <v>15577.772214</v>
       </c>
       <c r="Q104" t="n">
-        <v>14259.788349</v>
+        <v>14262.825012</v>
       </c>
       <c r="R104" t="n">
-        <v>13078.223382</v>
+        <v>13080.200962</v>
       </c>
       <c r="S104" t="n">
-        <v>12112.190261</v>
+        <v>12113.273583</v>
       </c>
       <c r="T104" t="n">
-        <v>11319.713996</v>
+        <v>11320.121044</v>
       </c>
       <c r="U104" t="n">
-        <v>10643.180387</v>
+        <v>10643.188746</v>
       </c>
       <c r="V104" t="n">
-        <v>10010.121023</v>
+        <v>10009.951941</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>7540.741529</v>
+        <v>7500.016064</v>
       </c>
       <c r="F105" t="n">
-        <v>7754.801111</v>
+        <v>7714.419812</v>
       </c>
       <c r="G105" t="n">
-        <v>8537.134177</v>
+        <v>8496.750893</v>
       </c>
       <c r="H105" t="n">
-        <v>9039.58474</v>
+        <v>8998.655014</v>
       </c>
       <c r="I105" t="n">
-        <v>9317.528167</v>
+        <v>9275.411298000001</v>
       </c>
       <c r="J105" t="n">
-        <v>10114.611319</v>
+        <v>10067.872826</v>
       </c>
       <c r="K105" t="n">
-        <v>11240.444067</v>
+        <v>11187.649551</v>
       </c>
       <c r="L105" t="n">
-        <v>11786.959332</v>
+        <v>11731.8042</v>
       </c>
       <c r="M105" t="n">
-        <v>11859.793747</v>
+        <v>11805.684737</v>
       </c>
       <c r="N105" t="n">
-        <v>11540.981208</v>
+        <v>11490.42277</v>
       </c>
       <c r="O105" t="n">
-        <v>11133.238644</v>
+        <v>11086.809439</v>
       </c>
       <c r="P105" t="n">
-        <v>10499.777028</v>
+        <v>10458.371538</v>
       </c>
       <c r="Q105" t="n">
-        <v>9963.869229</v>
+        <v>9927.011108000001</v>
       </c>
       <c r="R105" t="n">
-        <v>9453.571750999999</v>
+        <v>9421.115167</v>
       </c>
       <c r="S105" t="n">
-        <v>9038.701235</v>
+        <v>9010.339893</v>
       </c>
       <c r="T105" t="n">
-        <v>8700.197292000001</v>
+        <v>8675.743023000001</v>
       </c>
       <c r="U105" t="n">
-        <v>8414.545521</v>
+        <v>8393.940312999999</v>
       </c>
       <c r="V105" t="n">
-        <v>8147.870238</v>
+        <v>8131.122903</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>96838.631441</v>
+        <v>95776.702253</v>
       </c>
       <c r="F106" t="n">
-        <v>96267.02462500001</v>
+        <v>95580.646601</v>
       </c>
       <c r="G106" t="n">
-        <v>100271.423502</v>
+        <v>99846.92101999999</v>
       </c>
       <c r="H106" t="n">
-        <v>100577.237699</v>
+        <v>100328.510099</v>
       </c>
       <c r="I106" t="n">
-        <v>98439.699417</v>
+        <v>98296.567767</v>
       </c>
       <c r="J106" t="n">
-        <v>101566.398904</v>
+        <v>101474.942934</v>
       </c>
       <c r="K106" t="n">
-        <v>107389.435154</v>
+        <v>107322.822832</v>
       </c>
       <c r="L106" t="n">
-        <v>107436.396778</v>
+        <v>107382.241033</v>
       </c>
       <c r="M106" t="n">
-        <v>103494.70735</v>
+        <v>103446.73449</v>
       </c>
       <c r="N106" t="n">
-        <v>96743.90693</v>
+        <v>96699.48409899999</v>
       </c>
       <c r="O106" t="n">
-        <v>89887.716531</v>
+        <v>89845.11824700001</v>
       </c>
       <c r="P106" t="n">
-        <v>81836.660355</v>
+        <v>81795.72066000001</v>
       </c>
       <c r="Q106" t="n">
-        <v>75153.44335</v>
+        <v>75113.746369</v>
       </c>
       <c r="R106" t="n">
-        <v>69182.91936299999</v>
+        <v>69145.023414</v>
       </c>
       <c r="S106" t="n">
-        <v>64330.512207</v>
+        <v>64295.387426</v>
       </c>
       <c r="T106" t="n">
-        <v>60233.56858</v>
+        <v>60202.662396</v>
       </c>
       <c r="U106" t="n">
-        <v>56612.342643</v>
+        <v>56586.577142</v>
       </c>
       <c r="V106" t="n">
-        <v>53274.154749</v>
+        <v>53253.335197</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1046.943791</v>
+        <v>1074.522236</v>
       </c>
       <c r="F107" t="n">
-        <v>932.85031</v>
+        <v>959.450179</v>
       </c>
       <c r="G107" t="n">
-        <v>959.798936</v>
+        <v>985.508162</v>
       </c>
       <c r="H107" t="n">
-        <v>982.549698</v>
+        <v>1006.733643</v>
       </c>
       <c r="I107" t="n">
-        <v>992.268928</v>
+        <v>1014.832147</v>
       </c>
       <c r="J107" t="n">
-        <v>1058.986571</v>
+        <v>1081.500141</v>
       </c>
       <c r="K107" t="n">
-        <v>1158.437746</v>
+        <v>1181.656764</v>
       </c>
       <c r="L107" t="n">
-        <v>1198.15565</v>
+        <v>1220.862519</v>
       </c>
       <c r="M107" t="n">
-        <v>1192.31606</v>
+        <v>1213.631676</v>
       </c>
       <c r="N107" t="n">
-        <v>1149.734495</v>
+        <v>1169.020863</v>
       </c>
       <c r="O107" t="n">
-        <v>1098.547626</v>
+        <v>1115.752608</v>
       </c>
       <c r="P107" t="n">
-        <v>1023.663618</v>
+        <v>1038.529866</v>
       </c>
       <c r="Q107" t="n">
-        <v>956.798168</v>
+        <v>969.567261</v>
       </c>
       <c r="R107" t="n">
-        <v>891.5172659999999</v>
+        <v>902.326991</v>
       </c>
       <c r="S107" t="n">
-        <v>835.201048</v>
+        <v>844.263175</v>
       </c>
       <c r="T107" t="n">
-        <v>786.469741</v>
+        <v>793.949473</v>
       </c>
       <c r="U107" t="n">
-        <v>742.868146</v>
+        <v>748.897735</v>
       </c>
       <c r="V107" t="n">
-        <v>700.324161</v>
+        <v>704.998249</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>37086.474206</v>
+        <v>37739.232703</v>
       </c>
       <c r="F108" t="n">
-        <v>32481.760633</v>
+        <v>33029.478139</v>
       </c>
       <c r="G108" t="n">
-        <v>32792.124487</v>
+        <v>33275.42151</v>
       </c>
       <c r="H108" t="n">
-        <v>32748.141262</v>
+        <v>33169.122943</v>
       </c>
       <c r="I108" t="n">
-        <v>32126.499493</v>
+        <v>32490.361564</v>
       </c>
       <c r="J108" t="n">
-        <v>33257.600588</v>
+        <v>33595.180809</v>
       </c>
       <c r="K108" t="n">
-        <v>35312.021709</v>
+        <v>35637.92402</v>
       </c>
       <c r="L108" t="n">
-        <v>35542.760228</v>
+        <v>35844.111425</v>
       </c>
       <c r="M108" t="n">
-        <v>34553.41471</v>
+        <v>34823.470274</v>
       </c>
       <c r="N108" t="n">
-        <v>32688.07719</v>
+        <v>32923.591434</v>
       </c>
       <c r="O108" t="n">
-        <v>30816.429074</v>
+        <v>31020.781157</v>
       </c>
       <c r="P108" t="n">
-        <v>28484.962119</v>
+        <v>28658.689867</v>
       </c>
       <c r="Q108" t="n">
-        <v>26537.860757</v>
+        <v>26686.379474</v>
       </c>
       <c r="R108" t="n">
-        <v>24739.88142</v>
+        <v>24866.241691</v>
       </c>
       <c r="S108" t="n">
-        <v>23257.420107</v>
+        <v>23364.663051</v>
       </c>
       <c r="T108" t="n">
-        <v>22029.919247</v>
+        <v>22119.837469</v>
       </c>
       <c r="U108" t="n">
-        <v>20991.318035</v>
+        <v>21064.955222</v>
       </c>
       <c r="V108" t="n">
-        <v>20004.441215</v>
+        <v>20062.520029</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>19278.84098</v>
+        <v>19023.483377</v>
       </c>
       <c r="F109" t="n">
-        <v>19608.03524</v>
+        <v>19406.353899</v>
       </c>
       <c r="G109" t="n">
-        <v>20714.828336</v>
+        <v>20558.818044</v>
       </c>
       <c r="H109" t="n">
-        <v>20859.463748</v>
+        <v>20752.524857</v>
       </c>
       <c r="I109" t="n">
-        <v>20384.123405</v>
+        <v>20321.866351</v>
       </c>
       <c r="J109" t="n">
-        <v>20981.328145</v>
+        <v>20950.363052</v>
       </c>
       <c r="K109" t="n">
-        <v>22160.426244</v>
+        <v>22152.179574</v>
       </c>
       <c r="L109" t="n">
-        <v>22191.934113</v>
+        <v>22199.455091</v>
       </c>
       <c r="M109" t="n">
-        <v>21437.309798</v>
+        <v>21453.624487</v>
       </c>
       <c r="N109" t="n">
-        <v>20119.461678</v>
+        <v>20139.411702</v>
       </c>
       <c r="O109" t="n">
-        <v>18772.469451</v>
+        <v>18793.129368</v>
       </c>
       <c r="P109" t="n">
-        <v>17147.023148</v>
+        <v>17166.407573</v>
       </c>
       <c r="Q109" t="n">
-        <v>15773.970589</v>
+        <v>15791.367909</v>
       </c>
       <c r="R109" t="n">
-        <v>14530.987293</v>
+        <v>14545.936358</v>
       </c>
       <c r="S109" t="n">
-        <v>13517.263395</v>
+        <v>13529.792238</v>
       </c>
       <c r="T109" t="n">
-        <v>12682.707713</v>
+        <v>12693.010278</v>
       </c>
       <c r="U109" t="n">
-        <v>11971.412747</v>
+        <v>11979.743266</v>
       </c>
       <c r="V109" t="n">
-        <v>11306.740725</v>
+        <v>11313.269801</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16438.261959</v>
+        <v>16453.683138</v>
       </c>
       <c r="F110" t="n">
-        <v>16109.138595</v>
+        <v>16143.640587</v>
       </c>
       <c r="G110" t="n">
-        <v>17226.467708</v>
+        <v>17279.165928</v>
       </c>
       <c r="H110" t="n">
-        <v>17823.56787</v>
+        <v>17883.548041</v>
       </c>
       <c r="I110" t="n">
-        <v>17990.317425</v>
+        <v>18047.827888</v>
       </c>
       <c r="J110" t="n">
-        <v>19184.09245</v>
+        <v>19237.271247</v>
       </c>
       <c r="K110" t="n">
-        <v>21063.238392</v>
+        <v>21110.398064</v>
       </c>
       <c r="L110" t="n">
-        <v>21973.359304</v>
+        <v>22011.20488</v>
       </c>
       <c r="M110" t="n">
-        <v>22118.533788</v>
+        <v>22147.210825</v>
       </c>
       <c r="N110" t="n">
-        <v>21592.603654</v>
+        <v>21613.937328</v>
       </c>
       <c r="O110" t="n">
-        <v>20906.905558</v>
+        <v>20923.073616</v>
       </c>
       <c r="P110" t="n">
-        <v>19795.087874</v>
+        <v>19807.103998</v>
       </c>
       <c r="Q110" t="n">
-        <v>18869.74584</v>
+        <v>18878.419196</v>
       </c>
       <c r="R110" t="n">
-        <v>17988.397231</v>
+        <v>17994.255825</v>
       </c>
       <c r="S110" t="n">
-        <v>17269.145779</v>
+        <v>17272.852171</v>
       </c>
       <c r="T110" t="n">
-        <v>16671.654111</v>
+        <v>16673.784552</v>
       </c>
       <c r="U110" t="n">
-        <v>16156.003221</v>
+        <v>16156.997516</v>
       </c>
       <c r="V110" t="n">
-        <v>15650.019</v>
+        <v>15650.226703</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>83955.641046</v>
+        <v>83702.97649099999</v>
       </c>
       <c r="F111" t="n">
-        <v>82071.48010299999</v>
+        <v>81951.766009</v>
       </c>
       <c r="G111" t="n">
-        <v>86355.51053299999</v>
+        <v>86304.875676</v>
       </c>
       <c r="H111" t="n">
-        <v>87897.128698</v>
+        <v>87882.03095499999</v>
       </c>
       <c r="I111" t="n">
-        <v>87426.788911</v>
+        <v>87430.24360099999</v>
       </c>
       <c r="J111" t="n">
-        <v>91737.512712</v>
+        <v>91749.83585</v>
       </c>
       <c r="K111" t="n">
-        <v>98603.733792</v>
+        <v>98619.8708</v>
       </c>
       <c r="L111" t="n">
-        <v>100081.933641</v>
+        <v>100098.569347</v>
       </c>
       <c r="M111" t="n">
-        <v>97536.638425</v>
+        <v>97554.83427399999</v>
       </c>
       <c r="N111" t="n">
-        <v>91999.413967</v>
+        <v>92018.817434</v>
       </c>
       <c r="O111" t="n">
-        <v>86107.15577300001</v>
+        <v>86125.184286</v>
       </c>
       <c r="P111" t="n">
-        <v>78925.38237799999</v>
+        <v>78937.88569900001</v>
       </c>
       <c r="Q111" t="n">
-        <v>72938.173129</v>
+        <v>72943.037088</v>
       </c>
       <c r="R111" t="n">
-        <v>67515.480263</v>
+        <v>67512.833164</v>
       </c>
       <c r="S111" t="n">
-        <v>63104.050697</v>
+        <v>63095.611717</v>
       </c>
       <c r="T111" t="n">
-        <v>59394.203935</v>
+        <v>59382.877489</v>
       </c>
       <c r="U111" t="n">
-        <v>56123.904693</v>
+        <v>56112.294817</v>
       </c>
       <c r="V111" t="n">
-        <v>53090.29643</v>
+        <v>53079.434577</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>103615.103889</v>
+        <v>103275.952511</v>
       </c>
       <c r="F112" t="n">
-        <v>102569.81856</v>
+        <v>102397.697296</v>
       </c>
       <c r="G112" t="n">
-        <v>109289.143142</v>
+        <v>109257.940539</v>
       </c>
       <c r="H112" t="n">
-        <v>112387.135262</v>
+        <v>112453.427623</v>
       </c>
       <c r="I112" t="n">
-        <v>112573.018654</v>
+        <v>112696.281812</v>
       </c>
       <c r="J112" t="n">
-        <v>118767.767535</v>
+        <v>118926.803251</v>
       </c>
       <c r="K112" t="n">
-        <v>128593.652136</v>
+        <v>128775.158267</v>
       </c>
       <c r="L112" t="n">
-        <v>131940.918518</v>
+        <v>132123.768956</v>
       </c>
       <c r="M112" t="n">
-        <v>130515.420537</v>
+        <v>130686.964019</v>
       </c>
       <c r="N112" t="n">
-        <v>125298.443961</v>
+        <v>125454.1294</v>
       </c>
       <c r="O112" t="n">
-        <v>119551.101279</v>
+        <v>119692.504498</v>
       </c>
       <c r="P112" t="n">
-        <v>111671.044821</v>
+        <v>111797.67203</v>
       </c>
       <c r="Q112" t="n">
-        <v>105056.351803</v>
+        <v>105170.347844</v>
       </c>
       <c r="R112" t="n">
-        <v>98866.55394699999</v>
+        <v>98968.098241</v>
       </c>
       <c r="S112" t="n">
-        <v>93799.272755</v>
+        <v>93888.845271</v>
       </c>
       <c r="T112" t="n">
-        <v>89663.962567</v>
+        <v>89741.19288800001</v>
       </c>
       <c r="U112" t="n">
-        <v>86224.61010599999</v>
+        <v>86289.196839</v>
       </c>
       <c r="V112" t="n">
-        <v>83075.365897</v>
+        <v>83127.105425</v>
       </c>
     </row>
     <row r="113">
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>14976.99981</v>
+        <v>15281.095989</v>
       </c>
       <c r="F113" t="n">
-        <v>16529.352347</v>
+        <v>16489.139319</v>
       </c>
       <c r="G113" t="n">
-        <v>18251.470392</v>
+        <v>17576.918158</v>
       </c>
       <c r="H113" t="n">
-        <v>20315.53287</v>
+        <v>19076.718316</v>
       </c>
       <c r="I113" t="n">
-        <v>22342.989543</v>
+        <v>20699.123987</v>
       </c>
       <c r="J113" t="n">
-        <v>18353.820596</v>
+        <v>16929.07492</v>
       </c>
       <c r="K113" t="n">
-        <v>15918.719795</v>
+        <v>14693.794286</v>
       </c>
       <c r="L113" t="n">
-        <v>13791.575963</v>
+        <v>12768.195253</v>
       </c>
       <c r="M113" t="n">
-        <v>12359.315487</v>
+        <v>11482.027918</v>
       </c>
       <c r="N113" t="n">
-        <v>11357.392721</v>
+        <v>10586.102509</v>
       </c>
       <c r="O113" t="n">
-        <v>10324.358753</v>
+        <v>9651.067133</v>
       </c>
       <c r="P113" t="n">
-        <v>9394.782160999999</v>
+        <v>8806.608485999999</v>
       </c>
       <c r="Q113" t="n">
-        <v>8702.386168000001</v>
+        <v>8181.375839</v>
       </c>
       <c r="R113" t="n">
-        <v>8138.721981</v>
+        <v>7676.058956</v>
       </c>
       <c r="S113" t="n">
-        <v>7663.014497</v>
+        <v>7253.837621</v>
       </c>
       <c r="T113" t="n">
-        <v>7249.904366</v>
+        <v>6891.726697</v>
       </c>
       <c r="U113" t="n">
-        <v>6867.259817</v>
+        <v>6560.125237</v>
       </c>
       <c r="V113" t="n">
-        <v>6517.916053</v>
+        <v>6262.777249</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>5183.652888</v>
+        <v>4317.45383</v>
       </c>
       <c r="F114" t="n">
-        <v>5976.62749</v>
+        <v>5167.098378</v>
       </c>
       <c r="G114" t="n">
-        <v>6374.528193</v>
+        <v>5675.79038</v>
       </c>
       <c r="H114" t="n">
-        <v>6839.445608</v>
+        <v>6229.779219</v>
       </c>
       <c r="I114" t="n">
-        <v>7201.699315</v>
+        <v>6655.884044</v>
       </c>
       <c r="J114" t="n">
-        <v>5620.940387</v>
+        <v>5239.365064</v>
       </c>
       <c r="K114" t="n">
-        <v>4616.573748</v>
+        <v>4325.741353</v>
       </c>
       <c r="L114" t="n">
-        <v>3786.968101</v>
+        <v>3560.739167</v>
       </c>
       <c r="M114" t="n">
-        <v>3216.377279</v>
+        <v>3032.299373</v>
       </c>
       <c r="N114" t="n">
-        <v>2801.825533</v>
+        <v>2647.380009</v>
       </c>
       <c r="O114" t="n">
-        <v>2422.452657</v>
+        <v>2293.083431</v>
       </c>
       <c r="P114" t="n">
-        <v>2099.447078</v>
+        <v>1991.280844</v>
       </c>
       <c r="Q114" t="n">
-        <v>1852.967106</v>
+        <v>1761.745922</v>
       </c>
       <c r="R114" t="n">
-        <v>1654.468</v>
+        <v>1577.36252</v>
       </c>
       <c r="S114" t="n">
-        <v>1493.812782</v>
+        <v>1428.559659</v>
       </c>
       <c r="T114" t="n">
-        <v>1363.64171</v>
+        <v>1308.54275</v>
       </c>
       <c r="U114" t="n">
-        <v>1255.196389</v>
+        <v>1209.223961</v>
       </c>
       <c r="V114" t="n">
-        <v>1165.608178</v>
+        <v>1128.200613</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>88222.92769900001</v>
+        <v>88785.030577</v>
       </c>
       <c r="F115" t="n">
-        <v>100921.710566</v>
+        <v>101771.452707</v>
       </c>
       <c r="G115" t="n">
-        <v>115358.538064</v>
+        <v>116731.828111</v>
       </c>
       <c r="H115" t="n">
-        <v>129615.2508</v>
+        <v>131463.731743</v>
       </c>
       <c r="I115" t="n">
-        <v>141108.939687</v>
+        <v>143298.620514</v>
       </c>
       <c r="J115" t="n">
-        <v>113804.279336</v>
+        <v>115610.600334</v>
       </c>
       <c r="K115" t="n">
-        <v>96980.269315</v>
+        <v>98496.027218</v>
       </c>
       <c r="L115" t="n">
-        <v>82931.748697</v>
+        <v>84181.35834000001</v>
       </c>
       <c r="M115" t="n">
-        <v>73796.099347</v>
+        <v>74857.464821</v>
       </c>
       <c r="N115" t="n">
-        <v>67707.299958</v>
+        <v>68633.03569400001</v>
       </c>
       <c r="O115" t="n">
-        <v>61556.883935</v>
+        <v>62359.544781</v>
       </c>
       <c r="P115" t="n">
-        <v>56034.434192</v>
+        <v>56730.774101</v>
       </c>
       <c r="Q115" t="n">
-        <v>51878.596818</v>
+        <v>52490.828332</v>
       </c>
       <c r="R115" t="n">
-        <v>48418.24272</v>
+        <v>48958.011226</v>
       </c>
       <c r="S115" t="n">
-        <v>45399.96104</v>
+        <v>45874.391038</v>
       </c>
       <c r="T115" t="n">
-        <v>42644.637332</v>
+        <v>43057.913962</v>
       </c>
       <c r="U115" t="n">
-        <v>39958.541974</v>
+        <v>40311.648983</v>
       </c>
       <c r="V115" t="n">
-        <v>37376.317383</v>
+        <v>37668.863753</v>
       </c>
     </row>
     <row r="116">
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2473.093509</v>
+        <v>2388.354305</v>
       </c>
       <c r="F116" t="n">
-        <v>2949.539282</v>
+        <v>2826.645761</v>
       </c>
       <c r="G116" t="n">
-        <v>3450.935322</v>
+        <v>3301.130613</v>
       </c>
       <c r="H116" t="n">
-        <v>3835.392851</v>
+        <v>3667.732655</v>
       </c>
       <c r="I116" t="n">
-        <v>4169.560051</v>
+        <v>3987.925094</v>
       </c>
       <c r="J116" t="n">
-        <v>4086.706098</v>
+        <v>3910.103937</v>
       </c>
       <c r="K116" t="n">
-        <v>4109.140461</v>
+        <v>3933.482641</v>
       </c>
       <c r="L116" t="n">
-        <v>4041.639793</v>
+        <v>3871.25898</v>
       </c>
       <c r="M116" t="n">
-        <v>3918.632112</v>
+        <v>3756.248392</v>
       </c>
       <c r="N116" t="n">
-        <v>3739.935691</v>
+        <v>3586.939818</v>
       </c>
       <c r="O116" t="n">
-        <v>3546.693363</v>
+        <v>3403.275299</v>
       </c>
       <c r="P116" t="n">
-        <v>3337.27734</v>
+        <v>3204.363434</v>
       </c>
       <c r="Q116" t="n">
-        <v>3165.003821</v>
+        <v>3041.71462</v>
       </c>
       <c r="R116" t="n">
-        <v>3003.951077</v>
+        <v>2890.389201</v>
       </c>
       <c r="S116" t="n">
-        <v>2870.132466</v>
+        <v>2765.865352</v>
       </c>
       <c r="T116" t="n">
-        <v>2768.539178</v>
+        <v>2673.265638</v>
       </c>
       <c r="U116" t="n">
-        <v>2687.86258</v>
+        <v>2602.062138</v>
       </c>
       <c r="V116" t="n">
-        <v>2620.649277</v>
+        <v>2545.535338</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4777.298634</v>
+        <v>4767.331836</v>
       </c>
       <c r="F117" t="n">
-        <v>5698.015448</v>
+        <v>5731.331489</v>
       </c>
       <c r="G117" t="n">
-        <v>6383.055775</v>
+        <v>6451.996668</v>
       </c>
       <c r="H117" t="n">
-        <v>6723.305177</v>
+        <v>6814.98389</v>
       </c>
       <c r="I117" t="n">
-        <v>6903.943624</v>
+        <v>7007.320484</v>
       </c>
       <c r="J117" t="n">
-        <v>6390.760136</v>
+        <v>6489.182909</v>
       </c>
       <c r="K117" t="n">
-        <v>6080.711563</v>
+        <v>6173.535579</v>
       </c>
       <c r="L117" t="n">
-        <v>5672.198784</v>
+        <v>5756.484643</v>
       </c>
       <c r="M117" t="n">
-        <v>5223.871463</v>
+        <v>5297.964706</v>
       </c>
       <c r="N117" t="n">
-        <v>4742.225918</v>
+        <v>4801.394133</v>
       </c>
       <c r="O117" t="n">
-        <v>4292.845934</v>
+        <v>4337.502266</v>
       </c>
       <c r="P117" t="n">
-        <v>3871.763515</v>
+        <v>3904.778381</v>
       </c>
       <c r="Q117" t="n">
-        <v>3532.561851</v>
+        <v>3557.451501</v>
       </c>
       <c r="R117" t="n">
-        <v>3234.8484</v>
+        <v>3253.551695</v>
       </c>
       <c r="S117" t="n">
-        <v>2988.184403</v>
+        <v>3001.976271</v>
       </c>
       <c r="T117" t="n">
-        <v>2790.330409</v>
+        <v>2800.240032</v>
       </c>
       <c r="U117" t="n">
-        <v>2622.353591</v>
+        <v>2629.236245</v>
       </c>
       <c r="V117" t="n">
-        <v>2470.470379</v>
+        <v>2475.135593</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6286.210795</v>
+        <v>6314.579095</v>
       </c>
       <c r="F118" t="n">
-        <v>6231.018984</v>
+        <v>6267.051329</v>
       </c>
       <c r="G118" t="n">
-        <v>6445.73679</v>
+        <v>6479.143021</v>
       </c>
       <c r="H118" t="n">
-        <v>6555.932051</v>
+        <v>6581.764268</v>
       </c>
       <c r="I118" t="n">
-        <v>6670.544349</v>
+        <v>6686.968767</v>
       </c>
       <c r="J118" t="n">
-        <v>6211.352549</v>
+        <v>6216.850947</v>
       </c>
       <c r="K118" t="n">
-        <v>5996.36355</v>
+        <v>5991.985863</v>
       </c>
       <c r="L118" t="n">
-        <v>5705.437881</v>
+        <v>5692.251046</v>
       </c>
       <c r="M118" t="n">
-        <v>5385.207837</v>
+        <v>5364.839077</v>
       </c>
       <c r="N118" t="n">
-        <v>5026.807132</v>
+        <v>4997.111596</v>
       </c>
       <c r="O118" t="n">
-        <v>4686.099773</v>
+        <v>4648.162501</v>
       </c>
       <c r="P118" t="n">
-        <v>4355.788617</v>
+        <v>4312.633528</v>
       </c>
       <c r="Q118" t="n">
-        <v>4097.413843</v>
+        <v>4051.526301</v>
       </c>
       <c r="R118" t="n">
-        <v>3867.73026</v>
+        <v>3820.806673</v>
       </c>
       <c r="S118" t="n">
-        <v>3680.698522</v>
+        <v>3633.650536</v>
       </c>
       <c r="T118" t="n">
-        <v>3536.172972</v>
+        <v>3489.933955</v>
       </c>
       <c r="U118" t="n">
-        <v>3414.655218</v>
+        <v>3370.494402</v>
       </c>
       <c r="V118" t="n">
-        <v>3302.509014</v>
+        <v>3262.027487</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2140.762678</v>
+        <v>2118.231219</v>
       </c>
       <c r="F119" t="n">
-        <v>2552.070796</v>
+        <v>2533.31845</v>
       </c>
       <c r="G119" t="n">
-        <v>3019.243712</v>
+        <v>3011.815851</v>
       </c>
       <c r="H119" t="n">
-        <v>3375.053218</v>
+        <v>3379.602622</v>
       </c>
       <c r="I119" t="n">
-        <v>3663.639429</v>
+        <v>3676.647635</v>
       </c>
       <c r="J119" t="n">
-        <v>3570.935633</v>
+        <v>3586.865097</v>
       </c>
       <c r="K119" t="n">
-        <v>3567.525016</v>
+        <v>3583.333046</v>
       </c>
       <c r="L119" t="n">
-        <v>3489.522063</v>
+        <v>3503.183529</v>
       </c>
       <c r="M119" t="n">
-        <v>3369.070568</v>
+        <v>3379.641299</v>
       </c>
       <c r="N119" t="n">
-        <v>3204.856075</v>
+        <v>3209.606604</v>
       </c>
       <c r="O119" t="n">
-        <v>3029.15222</v>
+        <v>3028.104036</v>
       </c>
       <c r="P119" t="n">
-        <v>2840.82614</v>
+        <v>2835.361166</v>
       </c>
       <c r="Q119" t="n">
-        <v>2684.840328</v>
+        <v>2676.452687</v>
       </c>
       <c r="R119" t="n">
-        <v>2537.09916</v>
+        <v>2526.705641</v>
       </c>
       <c r="S119" t="n">
-        <v>2409.224507</v>
+        <v>2397.387404</v>
       </c>
       <c r="T119" t="n">
-        <v>2302.575808</v>
+        <v>2289.885122</v>
       </c>
       <c r="U119" t="n">
-        <v>2205.296624</v>
+        <v>2192.425066</v>
       </c>
       <c r="V119" t="n">
-        <v>2108.67371</v>
+        <v>2096.394225</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>153.810309</v>
+        <v>132.385806</v>
       </c>
       <c r="F120" t="n">
-        <v>253.985061</v>
+        <v>222.525453</v>
       </c>
       <c r="G120" t="n">
-        <v>341.09851</v>
+        <v>302.265571</v>
       </c>
       <c r="H120" t="n">
-        <v>413.302823</v>
+        <v>369.341495</v>
       </c>
       <c r="I120" t="n">
-        <v>479.452664</v>
+        <v>431.311048</v>
       </c>
       <c r="J120" t="n">
-        <v>496.170877</v>
+        <v>448.83492</v>
       </c>
       <c r="K120" t="n">
-        <v>523.209071</v>
+        <v>475.563047</v>
       </c>
       <c r="L120" t="n">
-        <v>537.640492</v>
+        <v>490.815886</v>
       </c>
       <c r="M120" t="n">
-        <v>543.0430679999999</v>
+        <v>497.761347</v>
       </c>
       <c r="N120" t="n">
-        <v>536.715334</v>
+        <v>493.429638</v>
       </c>
       <c r="O120" t="n">
-        <v>524.710239</v>
+        <v>483.608115</v>
       </c>
       <c r="P120" t="n">
-        <v>508.531745</v>
+        <v>469.96553</v>
       </c>
       <c r="Q120" t="n">
-        <v>497.178391</v>
+        <v>460.95692</v>
       </c>
       <c r="R120" t="n">
-        <v>486.786877</v>
+        <v>453.009865</v>
       </c>
       <c r="S120" t="n">
-        <v>480.005405</v>
+        <v>448.623792</v>
       </c>
       <c r="T120" t="n">
-        <v>477.812806</v>
+        <v>448.835951</v>
       </c>
       <c r="U120" t="n">
-        <v>478.368909</v>
+        <v>452.055217</v>
       </c>
       <c r="V120" t="n">
-        <v>480.248244</v>
+        <v>457.091219</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2366.034431</v>
+        <v>2036.465417</v>
       </c>
       <c r="F121" t="n">
-        <v>3721.017058</v>
+        <v>3260.116971</v>
       </c>
       <c r="G121" t="n">
-        <v>4815.511037</v>
+        <v>4267.280998</v>
       </c>
       <c r="H121" t="n">
-        <v>5699.273013</v>
+        <v>5093.064689</v>
       </c>
       <c r="I121" t="n">
-        <v>6517.518589</v>
+        <v>5863.097614</v>
       </c>
       <c r="J121" t="n">
-        <v>6684.568083</v>
+        <v>6046.843381</v>
       </c>
       <c r="K121" t="n">
-        <v>7009.393283</v>
+        <v>6371.083019</v>
       </c>
       <c r="L121" t="n">
-        <v>7177.559953</v>
+        <v>6552.44629</v>
       </c>
       <c r="M121" t="n">
-        <v>7232.943573</v>
+        <v>6629.823582</v>
       </c>
       <c r="N121" t="n">
-        <v>7152.142265</v>
+        <v>6575.327268</v>
       </c>
       <c r="O121" t="n">
-        <v>7000.283339</v>
+        <v>6451.930176</v>
       </c>
       <c r="P121" t="n">
-        <v>6786.217842</v>
+        <v>6271.562189</v>
       </c>
       <c r="Q121" t="n">
-        <v>6629.731022</v>
+        <v>6146.728103</v>
       </c>
       <c r="R121" t="n">
-        <v>6485.723208</v>
+        <v>6035.693928</v>
       </c>
       <c r="S121" t="n">
-        <v>6392.979577</v>
+        <v>5975.02176</v>
       </c>
       <c r="T121" t="n">
-        <v>6363.432289</v>
+        <v>5977.523305</v>
       </c>
       <c r="U121" t="n">
-        <v>6368.170076</v>
+        <v>6017.87543</v>
       </c>
       <c r="V121" t="n">
-        <v>6387.633311</v>
+        <v>6079.628893</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>117985.536793</v>
+        <v>118425.39947</v>
       </c>
       <c r="F122" t="n">
-        <v>124173.310843</v>
+        <v>124737.968018</v>
       </c>
       <c r="G122" t="n">
-        <v>137420.058448</v>
+        <v>138062.006871</v>
       </c>
       <c r="H122" t="n">
-        <v>148689.360068</v>
+        <v>149385.129582</v>
       </c>
       <c r="I122" t="n">
-        <v>159827.916999</v>
+        <v>160579.305063</v>
       </c>
       <c r="J122" t="n">
-        <v>156166.180157</v>
+        <v>156907.992342</v>
       </c>
       <c r="K122" t="n">
-        <v>157201.230165</v>
+        <v>157958.589915</v>
       </c>
       <c r="L122" t="n">
-        <v>154961.748053</v>
+        <v>155719.306644</v>
       </c>
       <c r="M122" t="n">
-        <v>150485.068256</v>
+        <v>151231.558473</v>
       </c>
       <c r="N122" t="n">
-        <v>144540.76754</v>
+        <v>145279.640897</v>
       </c>
       <c r="O122" t="n">
-        <v>138455.730133</v>
+        <v>139182.93261</v>
       </c>
       <c r="P122" t="n">
-        <v>131618.351243</v>
+        <v>132320.092214</v>
       </c>
       <c r="Q122" t="n">
-        <v>125901.137587</v>
+        <v>126573.036711</v>
       </c>
       <c r="R122" t="n">
-        <v>120326.343876</v>
+        <v>120962.325855</v>
       </c>
       <c r="S122" t="n">
-        <v>115506.111273</v>
+        <v>116104.811037</v>
       </c>
       <c r="T122" t="n">
-        <v>111578.018431</v>
+        <v>112137.19789</v>
       </c>
       <c r="U122" t="n">
-        <v>107956.47292</v>
+        <v>108469.031419</v>
       </c>
       <c r="V122" t="n">
-        <v>104192.792963</v>
+        <v>104647.164144</v>
       </c>
     </row>
     <row r="123">
@@ -9722,58 +9722,58 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1230.021435</v>
+        <v>1247.938424</v>
       </c>
       <c r="F123" t="n">
-        <v>1140.003138</v>
+        <v>1155.775241</v>
       </c>
       <c r="G123" t="n">
-        <v>1170.243222</v>
+        <v>1185.76993</v>
       </c>
       <c r="H123" t="n">
-        <v>1162.306775</v>
+        <v>1177.04322</v>
       </c>
       <c r="I123" t="n">
-        <v>1092.988995</v>
+        <v>1106.323973</v>
       </c>
       <c r="J123" t="n">
-        <v>1102.61616</v>
+        <v>1115.550727</v>
       </c>
       <c r="K123" t="n">
-        <v>1254.507486</v>
+        <v>1268.642577</v>
       </c>
       <c r="L123" t="n">
-        <v>1343.048642</v>
+        <v>1357.577494</v>
       </c>
       <c r="M123" t="n">
-        <v>1350.954431</v>
+        <v>1365.016488</v>
       </c>
       <c r="N123" t="n">
-        <v>1307.886653</v>
+        <v>1321.007334</v>
       </c>
       <c r="O123" t="n">
-        <v>1251.631693</v>
+        <v>1263.71319</v>
       </c>
       <c r="P123" t="n">
-        <v>1164.021486</v>
+        <v>1174.756078</v>
       </c>
       <c r="Q123" t="n">
-        <v>1082.116053</v>
+        <v>1091.544797</v>
       </c>
       <c r="R123" t="n">
-        <v>1006.51215</v>
+        <v>1014.689157</v>
       </c>
       <c r="S123" t="n">
-        <v>947.566324</v>
+        <v>954.633768</v>
       </c>
       <c r="T123" t="n">
-        <v>904.3922690000001</v>
+        <v>910.459789</v>
       </c>
       <c r="U123" t="n">
-        <v>869.264402</v>
+        <v>874.376129</v>
       </c>
       <c r="V123" t="n">
-        <v>835.865164</v>
+        <v>840.005229</v>
       </c>
     </row>
     <row r="124">
@@ -9798,58 +9798,58 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>16273.586982</v>
+        <v>16524.818843</v>
       </c>
       <c r="F124" t="n">
-        <v>14803.493434</v>
+        <v>15028.42548</v>
       </c>
       <c r="G124" t="n">
-        <v>14980.644735</v>
+        <v>15194.315381</v>
       </c>
       <c r="H124" t="n">
-        <v>14777.280833</v>
+        <v>14973.169247</v>
       </c>
       <c r="I124" t="n">
-        <v>13843.147993</v>
+        <v>14012.411768</v>
       </c>
       <c r="J124" t="n">
-        <v>13925.649273</v>
+        <v>14081.610032</v>
       </c>
       <c r="K124" t="n">
-        <v>15829.502856</v>
+        <v>15991.045049</v>
       </c>
       <c r="L124" t="n">
-        <v>16990.17974</v>
+        <v>17147.504022</v>
       </c>
       <c r="M124" t="n">
-        <v>17204.363246</v>
+        <v>17348.525326</v>
       </c>
       <c r="N124" t="n">
-        <v>16820.295752</v>
+        <v>16947.72684</v>
       </c>
       <c r="O124" t="n">
-        <v>16273.586683</v>
+        <v>16385.100997</v>
       </c>
       <c r="P124" t="n">
-        <v>15300.286304</v>
+        <v>15394.957734</v>
       </c>
       <c r="Q124" t="n">
-        <v>14376.397924</v>
+        <v>14456.306183</v>
       </c>
       <c r="R124" t="n">
-        <v>13519.189933</v>
+        <v>13586.129495</v>
       </c>
       <c r="S124" t="n">
-        <v>12873.171296</v>
+        <v>12929.30674</v>
       </c>
       <c r="T124" t="n">
-        <v>12430.377277</v>
+        <v>12477.277507</v>
       </c>
       <c r="U124" t="n">
-        <v>12095.171299</v>
+        <v>12133.714107</v>
       </c>
       <c r="V124" t="n">
-        <v>11758.866341</v>
+        <v>11789.43652</v>
       </c>
     </row>
     <row r="125">
@@ -9874,58 +9874,58 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>13276.041885</v>
+        <v>13006.893034</v>
       </c>
       <c r="F125" t="n">
-        <v>15124.018022</v>
+        <v>14883.313874</v>
       </c>
       <c r="G125" t="n">
-        <v>16897.052409</v>
+        <v>16667.855054</v>
       </c>
       <c r="H125" t="n">
-        <v>17624.12096</v>
+        <v>17413.4961</v>
       </c>
       <c r="I125" t="n">
-        <v>17068.236438</v>
+        <v>16885.637686</v>
       </c>
       <c r="J125" t="n">
-        <v>17492.175559</v>
+        <v>17323.280233</v>
       </c>
       <c r="K125" t="n">
-        <v>20051.555435</v>
+        <v>19875.87815</v>
       </c>
       <c r="L125" t="n">
-        <v>21548.553436</v>
+        <v>21376.700303</v>
       </c>
       <c r="M125" t="n">
-        <v>21729.838652</v>
+        <v>21571.614514</v>
       </c>
       <c r="N125" t="n">
-        <v>21085.208499</v>
+        <v>20944.65673</v>
       </c>
       <c r="O125" t="n">
-        <v>20211.3939</v>
+        <v>20087.798088</v>
       </c>
       <c r="P125" t="n">
-        <v>18825.423392</v>
+        <v>18720.01737</v>
       </c>
       <c r="Q125" t="n">
-        <v>17526.850994</v>
+        <v>17437.513991</v>
       </c>
       <c r="R125" t="n">
-        <v>16331.958323</v>
+        <v>16256.841755</v>
       </c>
       <c r="S125" t="n">
-        <v>15414.434411</v>
+        <v>15351.231524</v>
       </c>
       <c r="T125" t="n">
-        <v>14730.706754</v>
+        <v>14677.739003</v>
       </c>
       <c r="U125" t="n">
-        <v>14181.171988</v>
+        <v>14137.517453</v>
       </c>
       <c r="V125" t="n">
-        <v>13669.695063</v>
+        <v>13634.98482</v>
       </c>
     </row>
     <row r="126">
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>73451.87374700001</v>
+        <v>74604.642632</v>
       </c>
       <c r="F130" t="n">
-        <v>78335.991297</v>
+        <v>80353.797316</v>
       </c>
       <c r="G130" t="n">
-        <v>87929.953241</v>
+        <v>90805.49069200001</v>
       </c>
       <c r="H130" t="n">
-        <v>97268.468861</v>
+        <v>100940.508696</v>
       </c>
       <c r="I130" t="n">
-        <v>107406.118632</v>
+        <v>111883.846656</v>
       </c>
       <c r="J130" t="n">
-        <v>108797.140248</v>
+        <v>113686.605352</v>
       </c>
       <c r="K130" t="n">
-        <v>113694.36173</v>
+        <v>119116.742323</v>
       </c>
       <c r="L130" t="n">
-        <v>114506.64098</v>
+        <v>120252.770672</v>
       </c>
       <c r="M130" t="n">
-        <v>112073.47084</v>
+        <v>117956.077334</v>
       </c>
       <c r="N130" t="n">
-        <v>107218.648157</v>
+        <v>113079.661232</v>
       </c>
       <c r="O130" t="n">
-        <v>100577.285788</v>
+        <v>106286.647801</v>
       </c>
       <c r="P130" t="n">
-        <v>92529.329906</v>
+        <v>97967.83867500001</v>
       </c>
       <c r="Q130" t="n">
-        <v>84793.215811</v>
+        <v>89935.564103</v>
       </c>
       <c r="R130" t="n">
-        <v>77294.131416</v>
+        <v>82110.807845</v>
       </c>
       <c r="S130" t="n">
-        <v>70271.471726</v>
+        <v>74750.850313</v>
       </c>
       <c r="T130" t="n">
-        <v>63757.682564</v>
+        <v>67891.71286100001</v>
       </c>
       <c r="U130" t="n">
-        <v>57126.516424</v>
+        <v>60862.449937</v>
       </c>
       <c r="V130" t="n">
-        <v>50261.940412</v>
+        <v>53527.871903</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6709.251433</v>
+        <v>6777.759842</v>
       </c>
       <c r="F131" t="n">
-        <v>8128.742065</v>
+        <v>8275.352919999999</v>
       </c>
       <c r="G131" t="n">
-        <v>9350.479106999999</v>
+        <v>9559.144093999999</v>
       </c>
       <c r="H131" t="n">
-        <v>10356.86899</v>
+        <v>10611.805925</v>
       </c>
       <c r="I131" t="n">
-        <v>11473.71131</v>
+        <v>11771.662863</v>
       </c>
       <c r="J131" t="n">
-        <v>11808.862989</v>
+        <v>12127.690865</v>
       </c>
       <c r="K131" t="n">
-        <v>12646.56859</v>
+        <v>12998.292167</v>
       </c>
       <c r="L131" t="n">
-        <v>13107.129519</v>
+        <v>13481.210342</v>
       </c>
       <c r="M131" t="n">
-        <v>13195.536715</v>
+        <v>13579.547604</v>
       </c>
       <c r="N131" t="n">
-        <v>12958.733747</v>
+        <v>13340.103824</v>
       </c>
       <c r="O131" t="n">
-        <v>12500.041217</v>
+        <v>12869.300163</v>
       </c>
       <c r="P131" t="n">
-        <v>11854.917739</v>
+        <v>12202.334797</v>
       </c>
       <c r="Q131" t="n">
-        <v>11216.459502</v>
+        <v>11537.613308</v>
       </c>
       <c r="R131" t="n">
-        <v>10553.952913</v>
+        <v>10843.511401</v>
       </c>
       <c r="S131" t="n">
-        <v>9917.91541</v>
+        <v>10173.396396</v>
       </c>
       <c r="T131" t="n">
-        <v>9348.802928999999</v>
+        <v>9570.239283000001</v>
       </c>
       <c r="U131" t="n">
-        <v>8794.024589000001</v>
+        <v>8981.110707</v>
       </c>
       <c r="V131" t="n">
-        <v>8247.061159000001</v>
+        <v>8399.784023</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>159945.390525</v>
+        <v>159266.111102</v>
       </c>
       <c r="F132" t="n">
-        <v>173444.030924</v>
+        <v>172227.031636</v>
       </c>
       <c r="G132" t="n">
-        <v>190188.766451</v>
+        <v>188234.915129</v>
       </c>
       <c r="H132" t="n">
-        <v>203203.809195</v>
+        <v>200485.931291</v>
       </c>
       <c r="I132" t="n">
-        <v>219461.330542</v>
+        <v>216101.012188</v>
       </c>
       <c r="J132" t="n">
-        <v>221751.386139</v>
+        <v>218259.252645</v>
       </c>
       <c r="K132" t="n">
-        <v>234235.696931</v>
+        <v>230715.636603</v>
       </c>
       <c r="L132" t="n">
-        <v>239864.111541</v>
+        <v>236575.322067</v>
       </c>
       <c r="M132" t="n">
-        <v>238635.650679</v>
+        <v>235695.802433</v>
       </c>
       <c r="N132" t="n">
-        <v>231459.853767</v>
+        <v>228886.809648</v>
       </c>
       <c r="O132" t="n">
-        <v>220611.194434</v>
+        <v>218362.677077</v>
       </c>
       <c r="P132" t="n">
-        <v>206791.460002</v>
+        <v>204797.989081</v>
       </c>
       <c r="Q132" t="n">
-        <v>193577.045412</v>
+        <v>191739.050576</v>
       </c>
       <c r="R132" t="n">
-        <v>180872.826705</v>
+        <v>179143.187848</v>
       </c>
       <c r="S132" t="n">
-        <v>169831.455303</v>
+        <v>168196.26965</v>
       </c>
       <c r="T132" t="n">
-        <v>161271.381803</v>
+        <v>159734.683372</v>
       </c>
       <c r="U132" t="n">
-        <v>154188.870932</v>
+        <v>152779.39731</v>
       </c>
       <c r="V132" t="n">
-        <v>148268.810084</v>
+        <v>147028.626426</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>52007.724339</v>
+        <v>50999.988284</v>
       </c>
       <c r="F133" t="n">
-        <v>78792.898583</v>
+        <v>77730.474451</v>
       </c>
       <c r="G133" t="n">
-        <v>111425.869382</v>
+        <v>110864.614942</v>
       </c>
       <c r="H133" t="n">
-        <v>140552.539247</v>
+        <v>140585.402821</v>
       </c>
       <c r="I133" t="n">
-        <v>166557.057075</v>
+        <v>166937.370975</v>
       </c>
       <c r="J133" t="n">
-        <v>176489.74403</v>
+        <v>176905.161515</v>
       </c>
       <c r="K133" t="n">
-        <v>191680.468453</v>
+        <v>191994.941964</v>
       </c>
       <c r="L133" t="n">
-        <v>201188.656338</v>
+        <v>201376.811357</v>
       </c>
       <c r="M133" t="n">
-        <v>206367.472381</v>
+        <v>206476.407343</v>
       </c>
       <c r="N133" t="n">
-        <v>207933.1111</v>
+        <v>208028.316142</v>
       </c>
       <c r="O133" t="n">
-        <v>207031.856376</v>
+        <v>207167.419779</v>
       </c>
       <c r="P133" t="n">
-        <v>203756.29413</v>
+        <v>203969.036967</v>
       </c>
       <c r="Q133" t="n">
-        <v>200931.440331</v>
+        <v>201268.112092</v>
       </c>
       <c r="R133" t="n">
-        <v>197726.544321</v>
+        <v>198200.332827</v>
       </c>
       <c r="S133" t="n">
-        <v>194516.791354</v>
+        <v>195124.732548</v>
       </c>
       <c r="T133" t="n">
-        <v>191832.316559</v>
+        <v>192552.223156</v>
       </c>
       <c r="U133" t="n">
-        <v>188571.559232</v>
+        <v>189368.345971</v>
       </c>
       <c r="V133" t="n">
-        <v>184663.764137</v>
+        <v>185489.41761</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>9289.322441</v>
+        <v>9113.071619</v>
       </c>
       <c r="F134" t="n">
-        <v>10733.544348</v>
+        <v>10380.292261</v>
       </c>
       <c r="G134" t="n">
-        <v>12908.616047</v>
+        <v>12353.869045</v>
       </c>
       <c r="H134" t="n">
-        <v>15259.29684</v>
+        <v>14512.757482</v>
       </c>
       <c r="I134" t="n">
-        <v>18074.755377</v>
+        <v>17135.589481</v>
       </c>
       <c r="J134" t="n">
-        <v>19791.610488</v>
+        <v>18738.798309</v>
       </c>
       <c r="K134" t="n">
-        <v>22471.79371</v>
+        <v>21270.258549</v>
       </c>
       <c r="L134" t="n">
-        <v>24699.64137</v>
+        <v>23387.979602</v>
       </c>
       <c r="M134" t="n">
-        <v>26450.912333</v>
+        <v>25065.831446</v>
       </c>
       <c r="N134" t="n">
-        <v>27757.638767</v>
+        <v>26334.32823</v>
       </c>
       <c r="O134" t="n">
-        <v>28846.499996</v>
+        <v>27410.119502</v>
       </c>
       <c r="P134" t="n">
-        <v>29689.045379</v>
+        <v>28267.08876</v>
       </c>
       <c r="Q134" t="n">
-        <v>30686.326839</v>
+        <v>29284.977364</v>
       </c>
       <c r="R134" t="n">
-        <v>31728.831044</v>
+        <v>30356.729786</v>
       </c>
       <c r="S134" t="n">
-        <v>32938.376695</v>
+        <v>31600.863923</v>
       </c>
       <c r="T134" t="n">
-        <v>34479.086236</v>
+        <v>33181.61891</v>
       </c>
       <c r="U134" t="n">
-        <v>36223.672708</v>
+        <v>34987.255806</v>
       </c>
       <c r="V134" t="n">
-        <v>38191.119614</v>
+        <v>37048.250324</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5598.600378</v>
+        <v>5297.68015</v>
       </c>
       <c r="F135" t="n">
-        <v>8539.222276</v>
+        <v>8045.039701</v>
       </c>
       <c r="G135" t="n">
-        <v>11884.155649</v>
+        <v>11225.882874</v>
       </c>
       <c r="H135" t="n">
-        <v>15074.925031</v>
+        <v>14276.037479</v>
       </c>
       <c r="I135" t="n">
-        <v>18447.855241</v>
+        <v>17500.857778</v>
       </c>
       <c r="J135" t="n">
-        <v>20460.821031</v>
+        <v>19435.147249</v>
       </c>
       <c r="K135" t="n">
-        <v>23297.237275</v>
+        <v>22153.944275</v>
       </c>
       <c r="L135" t="n">
-        <v>25564.343066</v>
+        <v>24338.879285</v>
       </c>
       <c r="M135" t="n">
-        <v>27236.904173</v>
+        <v>25966.92749</v>
       </c>
       <c r="N135" t="n">
-        <v>28328.916631</v>
+        <v>27048.908311</v>
       </c>
       <c r="O135" t="n">
-        <v>28941.807083</v>
+        <v>27680.757316</v>
       </c>
       <c r="P135" t="n">
-        <v>29049.322021</v>
+        <v>27833.024147</v>
       </c>
       <c r="Q135" t="n">
-        <v>29091.347787</v>
+        <v>27923.538135</v>
       </c>
       <c r="R135" t="n">
-        <v>29023.569659</v>
+        <v>27907.968327</v>
       </c>
       <c r="S135" t="n">
-        <v>28968.436869</v>
+        <v>27907.789417</v>
       </c>
       <c r="T135" t="n">
-        <v>29063.679811</v>
+        <v>28061.961364</v>
       </c>
       <c r="U135" t="n">
-        <v>29162.646697</v>
+        <v>28236.926668</v>
       </c>
       <c r="V135" t="n">
-        <v>29323.79105</v>
+        <v>28495.430676</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>23398.90262</v>
+        <v>23758.950556</v>
       </c>
       <c r="F136" t="n">
-        <v>21718.916737</v>
+        <v>22228.231705</v>
       </c>
       <c r="G136" t="n">
-        <v>20328.65238</v>
+        <v>20846.927188</v>
       </c>
       <c r="H136" t="n">
-        <v>19138.712986</v>
+        <v>19584.607407</v>
       </c>
       <c r="I136" t="n">
-        <v>19457.241444</v>
+        <v>19858.066605</v>
       </c>
       <c r="J136" t="n">
-        <v>19251.802343</v>
+        <v>19616.108842</v>
       </c>
       <c r="K136" t="n">
-        <v>20319.922379</v>
+        <v>20692.777348</v>
       </c>
       <c r="L136" t="n">
-        <v>21106.873911</v>
+        <v>21505.388179</v>
       </c>
       <c r="M136" t="n">
-        <v>21562.690791</v>
+        <v>21999.519413</v>
       </c>
       <c r="N136" t="n">
-        <v>21522.374776</v>
+        <v>21987.263559</v>
       </c>
       <c r="O136" t="n">
-        <v>21058.852043</v>
+        <v>21538.046549</v>
       </c>
       <c r="P136" t="n">
-        <v>20207.347111</v>
+        <v>20685.343215</v>
       </c>
       <c r="Q136" t="n">
-        <v>19305.442887</v>
+        <v>19773.399754</v>
       </c>
       <c r="R136" t="n">
-        <v>18318.57885</v>
+        <v>18766.06299</v>
       </c>
       <c r="S136" t="n">
-        <v>17336.224184</v>
+        <v>17756.109229</v>
       </c>
       <c r="T136" t="n">
-        <v>16416.170755</v>
+        <v>16803.960924</v>
       </c>
       <c r="U136" t="n">
-        <v>15457.592443</v>
+        <v>15807.101556</v>
       </c>
       <c r="V136" t="n">
-        <v>14449.561236</v>
+        <v>14753.998899</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>3697.212283</v>
+        <v>3561.213358</v>
       </c>
       <c r="F137" t="n">
-        <v>4684.950017</v>
+        <v>4470.301866</v>
       </c>
       <c r="G137" t="n">
-        <v>5634.553441</v>
+        <v>5344.252447</v>
       </c>
       <c r="H137" t="n">
-        <v>6448.082996</v>
+        <v>6096.040442</v>
       </c>
       <c r="I137" t="n">
-        <v>7289.029584</v>
+        <v>6883.592817</v>
       </c>
       <c r="J137" t="n">
-        <v>7559.583433</v>
+        <v>7141.608558</v>
       </c>
       <c r="K137" t="n">
-        <v>8098.474592</v>
+        <v>7658.33496</v>
       </c>
       <c r="L137" t="n">
-        <v>8388.625553</v>
+        <v>7943.154031</v>
       </c>
       <c r="M137" t="n">
-        <v>8467.241453000001</v>
+        <v>8028.758678</v>
       </c>
       <c r="N137" t="n">
-        <v>8371.490248</v>
+        <v>7949.325092</v>
       </c>
       <c r="O137" t="n">
-        <v>8163.987712</v>
+        <v>7765.665131</v>
       </c>
       <c r="P137" t="n">
-        <v>7858.791554</v>
+        <v>7490.947796</v>
       </c>
       <c r="Q137" t="n">
-        <v>7582.26812</v>
+        <v>7244.553664</v>
       </c>
       <c r="R137" t="n">
-        <v>7315.097056</v>
+        <v>7006.926941</v>
       </c>
       <c r="S137" t="n">
-        <v>7087.026723</v>
+        <v>6806.815296</v>
       </c>
       <c r="T137" t="n">
-        <v>6926.092843</v>
+        <v>6672.33835</v>
       </c>
       <c r="U137" t="n">
-        <v>6794.802031</v>
+        <v>6569.007238</v>
       </c>
       <c r="V137" t="n">
-        <v>6699.395455</v>
+        <v>6504.164395</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>24964.609859</v>
+        <v>25342.781957</v>
       </c>
       <c r="F138" t="n">
-        <v>24821.603455</v>
+        <v>25424.441092</v>
       </c>
       <c r="G138" t="n">
-        <v>25587.281383</v>
+        <v>26339.356707</v>
       </c>
       <c r="H138" t="n">
-        <v>25905.18849</v>
+        <v>26727.432944</v>
       </c>
       <c r="I138" t="n">
-        <v>26458.964417</v>
+        <v>27318.031576</v>
       </c>
       <c r="J138" t="n">
-        <v>25342.589136</v>
+        <v>26164.177045</v>
       </c>
       <c r="K138" t="n">
-        <v>25613.484073</v>
+        <v>26436.683944</v>
       </c>
       <c r="L138" t="n">
-        <v>25355.971692</v>
+        <v>26163.678199</v>
       </c>
       <c r="M138" t="n">
-        <v>24989.346585</v>
+        <v>25798.978329</v>
       </c>
       <c r="N138" t="n">
-        <v>24437.525328</v>
+        <v>25258.085243</v>
       </c>
       <c r="O138" t="n">
-        <v>23667.608972</v>
+        <v>24499.73021</v>
       </c>
       <c r="P138" t="n">
-        <v>22559.962129</v>
+        <v>23387.261315</v>
       </c>
       <c r="Q138" t="n">
-        <v>21450.898112</v>
+        <v>22265.270988</v>
       </c>
       <c r="R138" t="n">
-        <v>20281.733943</v>
+        <v>21069.461725</v>
       </c>
       <c r="S138" t="n">
-        <v>19128.613769</v>
+        <v>19879.100071</v>
       </c>
       <c r="T138" t="n">
-        <v>18052.259886</v>
+        <v>18757.863891</v>
       </c>
       <c r="U138" t="n">
-        <v>16926.527897</v>
+        <v>17575.433203</v>
       </c>
       <c r="V138" t="n">
-        <v>15741.249385</v>
+        <v>16318.658646</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>55496.76467</v>
+        <v>56530.585678</v>
       </c>
       <c r="F139" t="n">
-        <v>57082.029281</v>
+        <v>58856.889812</v>
       </c>
       <c r="G139" t="n">
-        <v>62528.828798</v>
+        <v>65024.547333</v>
       </c>
       <c r="H139" t="n">
-        <v>68052.40399399999</v>
+        <v>71209.49896700001</v>
       </c>
       <c r="I139" t="n">
-        <v>74251.175334</v>
+        <v>78078.054865</v>
       </c>
       <c r="J139" t="n">
-        <v>74313.15612</v>
+        <v>78470.628948</v>
       </c>
       <c r="K139" t="n">
-        <v>76739.935296</v>
+        <v>81331.808305</v>
       </c>
       <c r="L139" t="n">
-        <v>76284.566828</v>
+        <v>81128.69863100001</v>
       </c>
       <c r="M139" t="n">
-        <v>73640.26710300001</v>
+        <v>78575.510928</v>
       </c>
       <c r="N139" t="n">
-        <v>69416.25131000001</v>
+        <v>74306.42801</v>
       </c>
       <c r="O139" t="n">
-        <v>64216.915299</v>
+        <v>68960.14445000001</v>
       </c>
       <c r="P139" t="n">
-        <v>58273.998881</v>
+        <v>62775.894532</v>
       </c>
       <c r="Q139" t="n">
-        <v>52636.336899</v>
+        <v>56877.808405</v>
       </c>
       <c r="R139" t="n">
-        <v>47235.715196</v>
+        <v>51193.452207</v>
       </c>
       <c r="S139" t="n">
-        <v>42226.510143</v>
+        <v>45895.750172</v>
       </c>
       <c r="T139" t="n">
-        <v>37598.035332</v>
+        <v>40978.688634</v>
       </c>
       <c r="U139" t="n">
-        <v>32939.246052</v>
+        <v>35995.029217</v>
       </c>
       <c r="V139" t="n">
-        <v>28140.671991</v>
+        <v>30817.536806</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>161818.956225</v>
+        <v>163759.011545</v>
       </c>
       <c r="F140" t="n">
-        <v>153457.227942</v>
+        <v>156015.193609</v>
       </c>
       <c r="G140" t="n">
-        <v>156881.220617</v>
+        <v>159582.537345</v>
       </c>
       <c r="H140" t="n">
-        <v>165078.368101</v>
+        <v>167816.427959</v>
       </c>
       <c r="I140" t="n">
-        <v>180219.857804</v>
+        <v>183158.245692</v>
       </c>
       <c r="J140" t="n">
-        <v>185139.53251</v>
+        <v>188212.002172</v>
       </c>
       <c r="K140" t="n">
-        <v>198225.524735</v>
+        <v>201601.932888</v>
       </c>
       <c r="L140" t="n">
-        <v>204916.47914</v>
+        <v>208444.937291</v>
       </c>
       <c r="M140" t="n">
-        <v>205434.098811</v>
+        <v>208905.416559</v>
       </c>
       <c r="N140" t="n">
-        <v>201007.258868</v>
+        <v>204259.710586</v>
       </c>
       <c r="O140" t="n">
-        <v>193884.190381</v>
+        <v>196863.612533</v>
       </c>
       <c r="P140" t="n">
-        <v>184880.542002</v>
+        <v>187603.653378</v>
       </c>
       <c r="Q140" t="n">
-        <v>176918.538582</v>
+        <v>179443.252549</v>
       </c>
       <c r="R140" t="n">
-        <v>169195.407885</v>
+        <v>171543.623528</v>
       </c>
       <c r="S140" t="n">
-        <v>161990.85413</v>
+        <v>164173.35274</v>
       </c>
       <c r="T140" t="n">
-        <v>155568.331592</v>
+        <v>157595.376868</v>
       </c>
       <c r="U140" t="n">
-        <v>148929.813376</v>
+        <v>150788.333712</v>
       </c>
       <c r="V140" t="n">
-        <v>141967.514031</v>
+        <v>143632.127069</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>12362.028589</v>
+        <v>11246.866328</v>
       </c>
       <c r="F141" t="n">
-        <v>19956.484959</v>
+        <v>18103.937834</v>
       </c>
       <c r="G141" t="n">
-        <v>27964.374241</v>
+        <v>25446.239371</v>
       </c>
       <c r="H141" t="n">
-        <v>35457.487865</v>
+        <v>32376.602087</v>
       </c>
       <c r="I141" t="n">
-        <v>43249.522051</v>
+        <v>39624.371284</v>
       </c>
       <c r="J141" t="n">
-        <v>47639.196326</v>
+        <v>43792.483211</v>
       </c>
       <c r="K141" t="n">
-        <v>53720.164944</v>
+        <v>49544.065544</v>
       </c>
       <c r="L141" t="n">
-        <v>58322.891997</v>
+        <v>53968.476876</v>
       </c>
       <c r="M141" t="n">
-        <v>61539.893467</v>
+        <v>57139.505677</v>
       </c>
       <c r="N141" t="n">
-        <v>63399.285091</v>
+        <v>59073.762897</v>
       </c>
       <c r="O141" t="n">
-        <v>64278.155605</v>
+        <v>60114.993632</v>
       </c>
       <c r="P141" t="n">
-        <v>64193.369271</v>
+        <v>60267.027967</v>
       </c>
       <c r="Q141" t="n">
-        <v>64133.573596</v>
+        <v>60448.182966</v>
       </c>
       <c r="R141" t="n">
-        <v>63765.953774</v>
+        <v>60351.585185</v>
       </c>
       <c r="S141" t="n">
-        <v>63431.528532</v>
+        <v>60294.170836</v>
       </c>
       <c r="T141" t="n">
-        <v>63491.05195</v>
+        <v>60623.206874</v>
       </c>
       <c r="U141" t="n">
-        <v>63756.882292</v>
+        <v>61173.046333</v>
       </c>
       <c r="V141" t="n">
-        <v>64354.907094</v>
+        <v>62085.141156</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>14799.14937</v>
+        <v>13281.123428</v>
       </c>
       <c r="F142" t="n">
-        <v>26068.792909</v>
+        <v>23653.450592</v>
       </c>
       <c r="G142" t="n">
-        <v>38466.240487</v>
+        <v>35451.214056</v>
       </c>
       <c r="H142" t="n">
-        <v>50856.773054</v>
+        <v>47429.872148</v>
       </c>
       <c r="I142" t="n">
-        <v>64178.145008</v>
+        <v>60274.061039</v>
       </c>
       <c r="J142" t="n">
-        <v>72754.446876</v>
+        <v>68550.206958</v>
       </c>
       <c r="K142" t="n">
-        <v>84269.80955000001</v>
+        <v>79498.02338899999</v>
       </c>
       <c r="L142" t="n">
-        <v>93823.02787799999</v>
+        <v>88561.65328</v>
       </c>
       <c r="M142" t="n">
-        <v>101213.902973</v>
+        <v>95619.105069</v>
       </c>
       <c r="N142" t="n">
-        <v>106428.905759</v>
+        <v>100687.290775</v>
       </c>
       <c r="O142" t="n">
-        <v>110185.332497</v>
+        <v>104444.61326</v>
       </c>
       <c r="P142" t="n">
-        <v>112447.866639</v>
+        <v>106844.806134</v>
       </c>
       <c r="Q142" t="n">
-        <v>114708.869286</v>
+        <v>109290.43926</v>
       </c>
       <c r="R142" t="n">
-        <v>116546.151816</v>
+        <v>111364.843966</v>
       </c>
       <c r="S142" t="n">
-        <v>118450.312453</v>
+        <v>113536.3167</v>
       </c>
       <c r="T142" t="n">
-        <v>120887.684541</v>
+        <v>116268.702316</v>
       </c>
       <c r="U142" t="n">
-        <v>123369.700627</v>
+        <v>119118.417642</v>
       </c>
       <c r="V142" t="n">
-        <v>126093.9687</v>
+        <v>122302.746415</v>
       </c>
     </row>
     <row r="143">
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>287.031255</v>
+        <v>269.477621</v>
       </c>
       <c r="F146" t="n">
-        <v>363.651075</v>
+        <v>336.598093</v>
       </c>
       <c r="G146" t="n">
-        <v>416.74326</v>
+        <v>383.284263</v>
       </c>
       <c r="H146" t="n">
-        <v>459.396734</v>
+        <v>421.545205</v>
       </c>
       <c r="I146" t="n">
-        <v>488.0546</v>
+        <v>447.899041</v>
       </c>
       <c r="J146" t="n">
-        <v>479.690515</v>
+        <v>440.835318</v>
       </c>
       <c r="K146" t="n">
-        <v>483.187328</v>
+        <v>444.934428</v>
       </c>
       <c r="L146" t="n">
-        <v>481.825173</v>
+        <v>444.523758</v>
       </c>
       <c r="M146" t="n">
-        <v>469.15083</v>
+        <v>433.558254</v>
       </c>
       <c r="N146" t="n">
-        <v>445.574697</v>
+        <v>412.390159</v>
       </c>
       <c r="O146" t="n">
-        <v>419.809432</v>
+        <v>389.055608</v>
       </c>
       <c r="P146" t="n">
-        <v>393.035465</v>
+        <v>364.652264</v>
       </c>
       <c r="Q146" t="n">
-        <v>370.642217</v>
+        <v>344.203435</v>
       </c>
       <c r="R146" t="n">
-        <v>350.055453</v>
+        <v>325.344298</v>
       </c>
       <c r="S146" t="n">
-        <v>332.417084</v>
+        <v>309.159786</v>
       </c>
       <c r="T146" t="n">
-        <v>318.044111</v>
+        <v>295.961077</v>
       </c>
       <c r="U146" t="n">
-        <v>305.344087</v>
+        <v>284.276348</v>
       </c>
       <c r="V146" t="n">
-        <v>296.032129</v>
+        <v>275.712357</v>
       </c>
     </row>
     <row r="147">
@@ -11546,58 +11546,58 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>154.159045</v>
+        <v>144.781298</v>
       </c>
       <c r="F147" t="n">
-        <v>203.115095</v>
+        <v>188.920745</v>
       </c>
       <c r="G147" t="n">
-        <v>237.904315</v>
+        <v>220.307031</v>
       </c>
       <c r="H147" t="n">
-        <v>268.438201</v>
+        <v>247.92462</v>
       </c>
       <c r="I147" t="n">
-        <v>293.524414</v>
+        <v>270.765719</v>
       </c>
       <c r="J147" t="n">
-        <v>298.380313</v>
+        <v>275.17722</v>
       </c>
       <c r="K147" t="n">
-        <v>311.888376</v>
+        <v>287.773332</v>
       </c>
       <c r="L147" t="n">
-        <v>323.019919</v>
+        <v>298.224879</v>
       </c>
       <c r="M147" t="n">
-        <v>326.910256</v>
+        <v>301.982432</v>
       </c>
       <c r="N147" t="n">
-        <v>322.974052</v>
+        <v>298.495304</v>
       </c>
       <c r="O147" t="n">
-        <v>315.345457</v>
+        <v>291.581825</v>
       </c>
       <c r="P147" t="n">
-        <v>304.660017</v>
+        <v>281.802907</v>
       </c>
       <c r="Q147" t="n">
-        <v>295.661986</v>
+        <v>273.534858</v>
       </c>
       <c r="R147" t="n">
-        <v>286.514575</v>
+        <v>265.095036</v>
       </c>
       <c r="S147" t="n">
-        <v>278.345568</v>
+        <v>257.544728</v>
       </c>
       <c r="T147" t="n">
-        <v>271.445786</v>
+        <v>251.167591</v>
       </c>
       <c r="U147" t="n">
-        <v>264.315363</v>
+        <v>244.580967</v>
       </c>
       <c r="V147" t="n">
-        <v>258.280438</v>
+        <v>239.014696</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>51926.355903</v>
+        <v>51953.287284</v>
       </c>
       <c r="F148" t="n">
-        <v>56754.356083</v>
+        <v>56795.603415</v>
       </c>
       <c r="G148" t="n">
-        <v>62630.801236</v>
+        <v>62681.857518</v>
       </c>
       <c r="H148" t="n">
-        <v>67852.378918</v>
+        <v>67910.74402699999</v>
       </c>
       <c r="I148" t="n">
-        <v>70965.023745</v>
+        <v>71027.937999</v>
       </c>
       <c r="J148" t="n">
-        <v>68820.09654699999</v>
+        <v>68882.154836</v>
       </c>
       <c r="K148" t="n">
-        <v>68644.479526</v>
+        <v>68706.847471</v>
       </c>
       <c r="L148" t="n">
-        <v>68553.550982</v>
+        <v>68615.647438</v>
       </c>
       <c r="M148" t="n">
-        <v>67503.644035</v>
+        <v>67564.164435</v>
       </c>
       <c r="N148" t="n">
-        <v>65216.01986</v>
+        <v>65273.683146</v>
       </c>
       <c r="O148" t="n">
-        <v>62410.6624</v>
+        <v>62465.179856</v>
       </c>
       <c r="P148" t="n">
-        <v>59271.257372</v>
+        <v>59322.497682</v>
       </c>
       <c r="Q148" t="n">
-        <v>56655.171146</v>
+        <v>56703.737056</v>
       </c>
       <c r="R148" t="n">
-        <v>54125.670904</v>
+        <v>54171.801599</v>
       </c>
       <c r="S148" t="n">
-        <v>51829.157863</v>
+        <v>51873.216001</v>
       </c>
       <c r="T148" t="n">
-        <v>49806.464991</v>
+        <v>49848.82622</v>
       </c>
       <c r="U148" t="n">
-        <v>47759.868347</v>
+        <v>47800.670483</v>
       </c>
       <c r="V148" t="n">
-        <v>45906.208813</v>
+        <v>45945.794327</v>
       </c>
     </row>
     <row r="149">
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5368.196761</v>
+        <v>5288.755865</v>
       </c>
       <c r="F149" t="n">
-        <v>6440.527505</v>
+        <v>6280.796779</v>
       </c>
       <c r="G149" t="n">
-        <v>8124.169216</v>
+        <v>7884.028574</v>
       </c>
       <c r="H149" t="n">
-        <v>9910.267422999999</v>
+        <v>9637.016541999999</v>
       </c>
       <c r="I149" t="n">
-        <v>11879.691885</v>
+        <v>11660.088331</v>
       </c>
       <c r="J149" t="n">
         <v>13906.551011</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>19942.948764</v>
+        <v>20297.851528</v>
       </c>
       <c r="F150" t="n">
-        <v>20567.307137</v>
+        <v>21141.428736</v>
       </c>
       <c r="G150" t="n">
-        <v>22519.980516</v>
+        <v>23297.196323</v>
       </c>
       <c r="H150" t="n">
-        <v>23486.083379</v>
+        <v>24358.131103</v>
       </c>
       <c r="I150" t="n">
-        <v>23467.465059</v>
+        <v>24200.152136</v>
       </c>
       <c r="J150" t="n">
         <v>21848.861464</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>10328.128841</v>
+        <v>10321.775587</v>
       </c>
       <c r="F151" t="n">
-        <v>12168.105605</v>
+        <v>12167.913137</v>
       </c>
       <c r="G151" t="n">
-        <v>14896.826405</v>
+        <v>14930.635657</v>
       </c>
       <c r="H151" t="n">
-        <v>17137.557718</v>
+        <v>17208.851295</v>
       </c>
       <c r="I151" t="n">
-        <v>18984.693846</v>
+        <v>19061.877203</v>
       </c>
       <c r="J151" t="n">
         <v>20251.355497</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>18739.954536</v>
+        <v>18642.41506</v>
       </c>
       <c r="F152" t="n">
-        <v>22517.394748</v>
+        <v>22411.804472</v>
       </c>
       <c r="G152" t="n">
-        <v>26827.450787</v>
+        <v>26694.035939</v>
       </c>
       <c r="H152" t="n">
-        <v>30168.024029</v>
+        <v>29999.315488</v>
       </c>
       <c r="I152" t="n">
-        <v>33202.597753</v>
+        <v>33040.059698</v>
       </c>
       <c r="J152" t="n">
         <v>35896.123164</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1563.407297</v>
+        <v>1419.190784</v>
       </c>
       <c r="F153" t="n">
-        <v>2437.863989</v>
+        <v>2170.172264</v>
       </c>
       <c r="G153" t="n">
-        <v>3705.499287</v>
+        <v>3320.398785</v>
       </c>
       <c r="H153" t="n">
-        <v>5203.085607</v>
+        <v>4760.090334</v>
       </c>
       <c r="I153" t="n">
-        <v>7060.302545</v>
+        <v>6682.968076</v>
       </c>
       <c r="J153" t="n">
         <v>9405.295443000001</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1792.344014</v>
+        <v>1764.991389</v>
       </c>
       <c r="F154" t="n">
-        <v>2170.497342</v>
+        <v>2129.580939</v>
       </c>
       <c r="G154" t="n">
-        <v>2624.312071</v>
+        <v>2571.943003</v>
       </c>
       <c r="H154" t="n">
-        <v>2986.075458</v>
+        <v>2927.688851</v>
       </c>
       <c r="I154" t="n">
-        <v>3332.122599</v>
+        <v>3281.728241</v>
       </c>
       <c r="J154" t="n">
         <v>3687.226347</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2857.995597</v>
+        <v>2852.191447</v>
       </c>
       <c r="F155" t="n">
-        <v>4528.507695</v>
+        <v>4506.46594</v>
       </c>
       <c r="G155" t="n">
-        <v>6936.674292</v>
+        <v>6872.900277</v>
       </c>
       <c r="H155" t="n">
-        <v>10006.410788</v>
+        <v>9844.594327000001</v>
       </c>
       <c r="I155" t="n">
-        <v>14271.804893</v>
+        <v>13854.354584</v>
       </c>
       <c r="J155" t="n">
         <v>23526.816635</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>26374.138775</v>
+        <v>26392.807172</v>
       </c>
       <c r="F156" t="n">
-        <v>39385.237395</v>
+        <v>39445.601424</v>
       </c>
       <c r="G156" t="n">
-        <v>56262.328339</v>
+        <v>56411.384885</v>
       </c>
       <c r="H156" t="n">
-        <v>74066.77639899999</v>
+        <v>74401.316101</v>
       </c>
       <c r="I156" t="n">
-        <v>92657.63255900001</v>
+        <v>93451.757872</v>
       </c>
       <c r="J156" t="n">
         <v>99708.75034100001</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>838.458977</v>
+        <v>841.9270310000001</v>
       </c>
       <c r="F157" t="n">
-        <v>1560.526411</v>
+        <v>1575.855113</v>
       </c>
       <c r="G157" t="n">
-        <v>2662.857944</v>
+        <v>2712.341151</v>
       </c>
       <c r="H157" t="n">
-        <v>3793.425927</v>
+        <v>3922.534519</v>
       </c>
       <c r="I157" t="n">
-        <v>4483.280167</v>
+        <v>4800.826175</v>
       </c>
       <c r="J157" t="n">
         <v>1480.975615</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2380.044459</v>
+        <v>2362.902054</v>
       </c>
       <c r="F158" t="n">
-        <v>3226.675521</v>
+        <v>3170.248516</v>
       </c>
       <c r="G158" t="n">
-        <v>4246.341221</v>
+        <v>4105.409925</v>
       </c>
       <c r="H158" t="n">
-        <v>5533.324527</v>
+        <v>5219.303238</v>
       </c>
       <c r="I158" t="n">
-        <v>7790.688513</v>
+        <v>7064.042428</v>
       </c>
       <c r="J158" t="n">
         <v>17517.08225</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>195.054178</v>
+        <v>195.65063</v>
       </c>
       <c r="F159" t="n">
-        <v>276.563829</v>
+        <v>278.440098</v>
       </c>
       <c r="G159" t="n">
-        <v>379.32018</v>
+        <v>383.917698</v>
       </c>
       <c r="H159" t="n">
-        <v>476.236525</v>
+        <v>486.305988</v>
       </c>
       <c r="I159" t="n">
-        <v>554.849547</v>
+        <v>577.860365</v>
       </c>
       <c r="J159" t="n">
         <v>374.365194</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4385.695704</v>
+        <v>4385.909358</v>
       </c>
       <c r="F160" t="n">
-        <v>6885.035393</v>
+        <v>6885.935154</v>
       </c>
       <c r="G160" t="n">
-        <v>10214.67633</v>
+        <v>10216.244372</v>
       </c>
       <c r="H160" t="n">
-        <v>13905.927376</v>
+        <v>13908.047366</v>
       </c>
       <c r="I160" t="n">
-        <v>18228.517901</v>
+        <v>18237.932155</v>
       </c>
       <c r="J160" t="n">
         <v>22238.187209</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>3698.326195</v>
+        <v>3775.547986</v>
       </c>
       <c r="F162" t="n">
-        <v>2700.372317</v>
+        <v>2801.070757</v>
       </c>
       <c r="G162" t="n">
-        <v>2066.001282</v>
+        <v>2167.454275</v>
       </c>
       <c r="H162" t="n">
-        <v>1712.942323</v>
+        <v>1812.387184</v>
       </c>
       <c r="I162" t="n">
-        <v>1469.335107</v>
+        <v>1560.059601</v>
       </c>
       <c r="J162" t="n">
         <v>1031.103893</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>354.9323</v>
+        <v>342.35637</v>
       </c>
       <c r="F163" t="n">
-        <v>510.353816</v>
+        <v>484.722728</v>
       </c>
       <c r="G163" t="n">
-        <v>721.4621550000001</v>
+        <v>682.452094</v>
       </c>
       <c r="H163" t="n">
-        <v>960.790448</v>
+        <v>908.76735</v>
       </c>
       <c r="I163" t="n">
-        <v>1263.555476</v>
+        <v>1206.248122</v>
       </c>
       <c r="J163" t="n">
         <v>1650.268884</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2417.397857</v>
+        <v>2159.405607</v>
       </c>
       <c r="F164" t="n">
-        <v>4497.526838</v>
+        <v>3941.646674</v>
       </c>
       <c r="G164" t="n">
-        <v>7446.846642</v>
+        <v>6538.606525</v>
       </c>
       <c r="H164" t="n">
-        <v>11518.011937</v>
+        <v>10242.000086</v>
       </c>
       <c r="I164" t="n">
-        <v>17712.100015</v>
+        <v>16259.124884</v>
       </c>
       <c r="J164" t="n">
         <v>27430.548299</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>3547.970538</v>
+        <v>3485.58772</v>
       </c>
       <c r="F165" t="n">
-        <v>4696.863202</v>
+        <v>4564.041773</v>
       </c>
       <c r="G165" t="n">
-        <v>5748.336628</v>
+        <v>5513.727905</v>
       </c>
       <c r="H165" t="n">
-        <v>7100.809224</v>
+        <v>6749.022378</v>
       </c>
       <c r="I165" t="n">
-        <v>9164.188625000001</v>
+        <v>8746.771895</v>
       </c>
       <c r="J165" t="n">
         <v>12169.861005</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>11013.115211</v>
+        <v>10309.948045</v>
       </c>
       <c r="F166" t="n">
-        <v>16327.21733</v>
+        <v>14868.832407</v>
       </c>
       <c r="G166" t="n">
-        <v>23211.183663</v>
+        <v>20904.134516</v>
       </c>
       <c r="H166" t="n">
-        <v>32404.347374</v>
+        <v>29244.737365</v>
       </c>
       <c r="I166" t="n">
-        <v>46183.341991</v>
+        <v>42673.826454</v>
       </c>
       <c r="J166" t="n">
         <v>67485.715364</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>86971.34364399999</v>
+        <v>88278.395901</v>
       </c>
       <c r="F167" t="n">
-        <v>91855.88787399999</v>
+        <v>94356.15917100001</v>
       </c>
       <c r="G167" t="n">
-        <v>97906.69558499999</v>
+        <v>101644.773923</v>
       </c>
       <c r="H167" t="n">
-        <v>102420.424433</v>
+        <v>107523.730138</v>
       </c>
       <c r="I167" t="n">
-        <v>100272.176058</v>
+        <v>106169.380601</v>
       </c>
       <c r="J167" t="n">
         <v>72774.560048</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1561.28234</v>
+        <v>1593.178271</v>
       </c>
       <c r="F168" t="n">
-        <v>1757.328975</v>
+        <v>1827.603101</v>
       </c>
       <c r="G168" t="n">
-        <v>1921.829861</v>
+        <v>2039.104827</v>
       </c>
       <c r="H168" t="n">
-        <v>1936.883985</v>
+        <v>2105.701705</v>
       </c>
       <c r="I168" t="n">
-        <v>1654.717069</v>
+        <v>1852.662005</v>
       </c>
       <c r="J168" t="n">
         <v>599.478651</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>35188.710252</v>
+        <v>33803.187361</v>
       </c>
       <c r="F169" t="n">
-        <v>50179.405647</v>
+        <v>47116.88314</v>
       </c>
       <c r="G169" t="n">
-        <v>70374.237802</v>
+        <v>65208.738781</v>
       </c>
       <c r="H169" t="n">
-        <v>98732.334825</v>
+        <v>91259.47521400001</v>
       </c>
       <c r="I169" t="n">
-        <v>142500.154979</v>
+        <v>133776.916143</v>
       </c>
       <c r="J169" t="n">
         <v>208742.405573</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1986.536891</v>
+        <v>1863.604191</v>
       </c>
       <c r="F170" t="n">
-        <v>3432.525857</v>
+        <v>3163.977367</v>
       </c>
       <c r="G170" t="n">
-        <v>5364.387143</v>
+        <v>4917.217571</v>
       </c>
       <c r="H170" t="n">
-        <v>7875.764741</v>
+        <v>7228.005773</v>
       </c>
       <c r="I170" t="n">
-        <v>11573.181057</v>
+        <v>10808.767669</v>
       </c>
       <c r="J170" t="n">
         <v>17231.304046</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>19099.84425</v>
+        <v>18953.89142</v>
       </c>
       <c r="F171" t="n">
-        <v>23061.298459</v>
+        <v>22764.101276</v>
       </c>
       <c r="G171" t="n">
-        <v>27636.119284</v>
+        <v>27167.350254</v>
       </c>
       <c r="H171" t="n">
-        <v>32360.627541</v>
+        <v>31720.531687</v>
       </c>
       <c r="I171" t="n">
-        <v>37772.971233</v>
+        <v>37065.709146</v>
       </c>
       <c r="J171" t="n">
         <v>42920.294374</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>28921.303429</v>
+        <v>29444.617036</v>
       </c>
       <c r="F172" t="n">
-        <v>29462.516611</v>
+        <v>30468.89314</v>
       </c>
       <c r="G172" t="n">
-        <v>28559.029774</v>
+        <v>29955.692842</v>
       </c>
       <c r="H172" t="n">
-        <v>26435.630191</v>
+        <v>28120.632204</v>
       </c>
       <c r="I172" t="n">
-        <v>22834.506917</v>
+        <v>24555.053107</v>
       </c>
       <c r="J172" t="n">
         <v>13886.841038</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>92.47576599999999</v>
+        <v>81.817098</v>
       </c>
       <c r="F173" t="n">
-        <v>181.06502</v>
+        <v>156.95184</v>
       </c>
       <c r="G173" t="n">
-        <v>309.647336</v>
+        <v>268.377731</v>
       </c>
       <c r="H173" t="n">
-        <v>497.893805</v>
+        <v>437.147253</v>
       </c>
       <c r="I173" t="n">
-        <v>807.305477</v>
+        <v>734.777912</v>
       </c>
       <c r="J173" t="n">
         <v>1332.143273</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>117876.451182</v>
+        <v>118930.481146</v>
       </c>
       <c r="F174" t="n">
-        <v>127277.816813</v>
+        <v>129252.813073</v>
       </c>
       <c r="G174" t="n">
-        <v>137220.927647</v>
+        <v>140043.767546</v>
       </c>
       <c r="H174" t="n">
-        <v>145282.110545</v>
+        <v>148956.016059</v>
       </c>
       <c r="I174" t="n">
-        <v>148710.406096</v>
+        <v>152827.823276</v>
       </c>
       <c r="J174" t="n">
         <v>130542.690751</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>348.137806</v>
+        <v>331.785816</v>
       </c>
       <c r="F175" t="n">
-        <v>641.805967</v>
+        <v>607.474831</v>
       </c>
       <c r="G175" t="n">
-        <v>1067.480588</v>
+        <v>1014.38002</v>
       </c>
       <c r="H175" t="n">
-        <v>1600.974113</v>
+        <v>1531.090342</v>
       </c>
       <c r="I175" t="n">
-        <v>2269.193448</v>
+        <v>2195.956282</v>
       </c>
       <c r="J175" t="n">
         <v>2994.773677</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>27.452047</v>
+        <v>25.371631</v>
       </c>
       <c r="F176" t="n">
-        <v>40.163122</v>
+        <v>35.856339</v>
       </c>
       <c r="G176" t="n">
-        <v>57.680202</v>
+        <v>50.883102</v>
       </c>
       <c r="H176" t="n">
-        <v>82.543702</v>
+        <v>73.24042</v>
       </c>
       <c r="I176" t="n">
-        <v>121.786654</v>
+        <v>111.420536</v>
       </c>
       <c r="J176" t="n">
         <v>184.645189</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>76274.040211</v>
+        <v>76009.063953</v>
       </c>
       <c r="F177" t="n">
-        <v>112160.376744</v>
+        <v>112390.894976</v>
       </c>
       <c r="G177" t="n">
-        <v>150068.752152</v>
+        <v>151596.068841</v>
       </c>
       <c r="H177" t="n">
-        <v>177582.959506</v>
+        <v>180638.570451</v>
       </c>
       <c r="I177" t="n">
-        <v>191395.92854</v>
+        <v>195213.90085</v>
       </c>
       <c r="J177" t="n">
         <v>177807.685696</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>46.739231</v>
+        <v>41.069713</v>
       </c>
       <c r="F178" t="n">
-        <v>89.77548299999999</v>
+        <v>77.053477</v>
       </c>
       <c r="G178" t="n">
-        <v>152.403449</v>
+        <v>130.734452</v>
       </c>
       <c r="H178" t="n">
-        <v>247.165701</v>
+        <v>215.30409</v>
       </c>
       <c r="I178" t="n">
-        <v>405.361678</v>
+        <v>367.365698</v>
       </c>
       <c r="J178" t="n">
         <v>677.617488</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>58.847392</v>
+        <v>55.597281</v>
       </c>
       <c r="F179" t="n">
-        <v>83.12056800000001</v>
+        <v>76.44457199999999</v>
       </c>
       <c r="G179" t="n">
-        <v>115.483061</v>
+        <v>105.039049</v>
       </c>
       <c r="H179" t="n">
-        <v>157.594938</v>
+        <v>143.449634</v>
       </c>
       <c r="I179" t="n">
-        <v>219.662377</v>
+        <v>204.108618</v>
       </c>
       <c r="J179" t="n">
         <v>312.342819</v>
@@ -14130,55 +14130,55 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="F181" t="n">
         <v>-2e-06</v>
       </c>
-      <c r="F181" t="n">
+      <c r="G181" t="n">
+        <v>-6e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1.1e-05</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="J181" t="n">
         <v>1e-06</v>
       </c>
-      <c r="G181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="H181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="I181" t="n">
-        <v>-2e-06</v>
-      </c>
-      <c r="J181" t="n">
-        <v>0</v>
-      </c>
       <c r="K181" t="n">
-        <v>-3e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="L181" t="n">
-        <v>-1e-06</v>
+        <v>-5e-06</v>
       </c>
       <c r="M181" t="n">
+        <v>4e-06</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="O181" t="n">
         <v>-4e-06</v>
       </c>
-      <c r="N181" t="n">
-        <v>2e-06</v>
-      </c>
-      <c r="O181" t="n">
+      <c r="P181" t="n">
         <v>3e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>0</v>
       </c>
       <c r="Q181" t="n">
         <v>2e-06</v>
       </c>
       <c r="R181" t="n">
-        <v>7e-06</v>
+        <v>1e-06</v>
       </c>
       <c r="S181" t="n">
-        <v>7e-06</v>
+        <v>4e-06</v>
       </c>
       <c r="T181" t="n">
         <v>1e-06</v>
       </c>
       <c r="U181" t="n">
-        <v>-7e-06</v>
+        <v>-4e-06</v>
       </c>
       <c r="V181" t="n">
         <v>-5e-06</v>
